--- a/logs/one_head_map_search_optimization/one_head_map_search_optimization.xlsx
+++ b/logs/one_head_map_search_optimization/one_head_map_search_optimization.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgep-my.sharepoint.com/personal/uxue_ballarin_alumni_mondragon_edu/Documents/Semestre 8-Erasmus/Simula/ship_qnn/logs/one_head_map_search_optimization/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="107" documentId="11_AD4D2F04E46CFB4ACB3E20D455D6CCDA693EDF1F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EBDCA932-0EBF-4234-9302-B2F918564CBE}"/>
+  <xr:revisionPtr revIDLastSave="116" documentId="11_AD4D2F04E46CFB4ACB3E20D455D6CCDA693EDF1F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3558DBD7-2E40-4DCE-AAAB-92D53675D2D6}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-5580" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main results" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="21" r:id="rId3"/>
+    <pivotCache cacheId="0" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2180" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2165" uniqueCount="256">
   <si>
     <t>date</t>
   </si>
@@ -854,7 +854,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -867,13 +867,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -9521,8 +9518,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{37B8E839-F96B-4695-BBD4-28D863AD6E55}" name="TablaDinámica1" cacheId="21" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:L49" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{37B8E839-F96B-4695-BBD4-28D863AD6E55}" name="TablaDinámica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:L64" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="75">
     <pivotField numFmtId="164" showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
@@ -9561,19 +9558,19 @@
     </pivotField>
     <pivotField axis="axisRow" showAll="0">
       <items count="3">
-        <item x="0"/>
-        <item x="1"/>
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
     <pivotField axis="axisRow" showAll="0">
       <items count="7">
-        <item sd="0" x="2"/>
-        <item sd="0" x="5"/>
-        <item sd="0" x="1"/>
-        <item sd="0" x="0"/>
-        <item sd="0" x="3"/>
-        <item sd="0" x="4"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="4"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -9631,12 +9628,12 @@
     <pivotField dataField="1" showAll="0"/>
   </pivotFields>
   <rowFields count="4">
+    <field x="22"/>
     <field x="20"/>
     <field x="21"/>
-    <field x="22"/>
     <field x="2"/>
   </rowFields>
-  <rowItems count="46">
+  <rowItems count="61">
     <i>
       <x/>
     </i>
@@ -9649,18 +9646,6 @@
     <i r="2">
       <x v="1"/>
     </i>
-    <i r="2">
-      <x v="2"/>
-    </i>
-    <i r="2">
-      <x v="3"/>
-    </i>
-    <i r="2">
-      <x v="4"/>
-    </i>
-    <i r="2">
-      <x v="5"/>
-    </i>
     <i r="1">
       <x v="1"/>
     </i>
@@ -9670,17 +9655,14 @@
     <i r="2">
       <x v="1"/>
     </i>
-    <i r="2">
+    <i r="1">
       <x v="2"/>
     </i>
     <i r="2">
-      <x v="3"/>
+      <x/>
     </i>
     <i r="2">
-      <x v="4"/>
-    </i>
-    <i r="2">
-      <x v="5"/>
+      <x v="1"/>
     </i>
     <i>
       <x v="1"/>
@@ -9694,18 +9676,6 @@
     <i r="2">
       <x v="1"/>
     </i>
-    <i r="2">
-      <x v="2"/>
-    </i>
-    <i r="2">
-      <x v="3"/>
-    </i>
-    <i r="2">
-      <x v="4"/>
-    </i>
-    <i r="2">
-      <x v="5"/>
-    </i>
     <i r="1">
       <x v="1"/>
     </i>
@@ -9715,17 +9685,14 @@
     <i r="2">
       <x v="1"/>
     </i>
-    <i r="2">
+    <i r="1">
       <x v="2"/>
     </i>
     <i r="2">
-      <x v="3"/>
+      <x/>
     </i>
     <i r="2">
-      <x v="4"/>
-    </i>
-    <i r="2">
-      <x v="5"/>
+      <x v="1"/>
     </i>
     <i>
       <x v="2"/>
@@ -9739,17 +9706,35 @@
     <i r="2">
       <x v="1"/>
     </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
     <i r="2">
+      <x/>
+    </i>
+    <i r="2">
+      <x v="1"/>
+    </i>
+    <i r="1">
       <x v="2"/>
     </i>
     <i r="2">
+      <x/>
+    </i>
+    <i r="2">
+      <x v="1"/>
+    </i>
+    <i>
       <x v="3"/>
     </i>
-    <i r="2">
-      <x v="4"/>
+    <i r="1">
+      <x/>
     </i>
     <i r="2">
-      <x v="5"/>
+      <x/>
+    </i>
+    <i r="2">
+      <x v="1"/>
     </i>
     <i r="1">
       <x v="1"/>
@@ -9760,17 +9745,74 @@
     <i r="2">
       <x v="1"/>
     </i>
-    <i r="2">
+    <i r="1">
       <x v="2"/>
     </i>
     <i r="2">
-      <x v="3"/>
+      <x/>
     </i>
     <i r="2">
+      <x v="1"/>
+    </i>
+    <i>
       <x v="4"/>
     </i>
+    <i r="1">
+      <x/>
+    </i>
     <i r="2">
+      <x/>
+    </i>
+    <i r="2">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="2">
+      <x/>
+    </i>
+    <i r="2">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="2">
+      <x/>
+    </i>
+    <i r="2">
+      <x v="1"/>
+    </i>
+    <i>
       <x v="5"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="2">
+      <x/>
+    </i>
+    <i r="2">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="2">
+      <x/>
+    </i>
+    <i r="2">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="2">
+      <x/>
+    </i>
+    <i r="2">
+      <x v="1"/>
     </i>
     <i t="grand">
       <x/>
@@ -10321,7 +10363,7 @@
       <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="8" t="s">
+      <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
       <c r="W1" s="2" t="s">
@@ -10548,7 +10590,7 @@
       <c r="U2" t="s">
         <v>98</v>
       </c>
-      <c r="V2" s="6">
+      <c r="V2">
         <v>1</v>
       </c>
       <c r="W2" t="s">
@@ -10772,7 +10814,7 @@
       <c r="U3" t="s">
         <v>87</v>
       </c>
-      <c r="V3" s="6">
+      <c r="V3">
         <v>1</v>
       </c>
       <c r="W3" t="s">
@@ -10996,7 +11038,7 @@
       <c r="U4" t="s">
         <v>95</v>
       </c>
-      <c r="V4" s="6">
+      <c r="V4">
         <v>1</v>
       </c>
       <c r="W4" t="s">
@@ -11220,7 +11262,7 @@
       <c r="U5" t="s">
         <v>98</v>
       </c>
-      <c r="V5" s="6">
+      <c r="V5">
         <v>1</v>
       </c>
       <c r="W5" t="s">
@@ -11444,7 +11486,7 @@
       <c r="U6" t="s">
         <v>98</v>
       </c>
-      <c r="V6" s="6">
+      <c r="V6">
         <v>1</v>
       </c>
       <c r="W6" t="s">
@@ -11668,7 +11710,7 @@
       <c r="U7" t="s">
         <v>98</v>
       </c>
-      <c r="V7" s="6">
+      <c r="V7">
         <v>1</v>
       </c>
       <c r="W7" t="s">
@@ -11892,7 +11934,7 @@
       <c r="U8" t="s">
         <v>95</v>
       </c>
-      <c r="V8" s="6">
+      <c r="V8">
         <v>1</v>
       </c>
       <c r="W8" t="s">
@@ -12116,7 +12158,7 @@
       <c r="U9" t="s">
         <v>87</v>
       </c>
-      <c r="V9" s="6">
+      <c r="V9">
         <v>1</v>
       </c>
       <c r="W9" t="s">
@@ -12340,7 +12382,7 @@
       <c r="U10" t="s">
         <v>98</v>
       </c>
-      <c r="V10" s="6">
+      <c r="V10">
         <v>1</v>
       </c>
       <c r="W10" t="s">
@@ -12564,7 +12606,7 @@
       <c r="U11" t="s">
         <v>95</v>
       </c>
-      <c r="V11" s="6">
+      <c r="V11">
         <v>1</v>
       </c>
       <c r="W11" t="s">
@@ -12788,7 +12830,7 @@
       <c r="U12" t="s">
         <v>95</v>
       </c>
-      <c r="V12" s="6">
+      <c r="V12">
         <v>1</v>
       </c>
       <c r="W12" t="s">
@@ -13012,7 +13054,7 @@
       <c r="U13" t="s">
         <v>95</v>
       </c>
-      <c r="V13" s="6">
+      <c r="V13">
         <v>1</v>
       </c>
       <c r="W13" t="s">
@@ -13236,7 +13278,7 @@
       <c r="U14" t="s">
         <v>87</v>
       </c>
-      <c r="V14" s="6">
+      <c r="V14">
         <v>1</v>
       </c>
       <c r="W14" t="s">
@@ -13460,7 +13502,7 @@
       <c r="U15" t="s">
         <v>98</v>
       </c>
-      <c r="V15" s="6">
+      <c r="V15">
         <v>1</v>
       </c>
       <c r="W15" t="s">
@@ -13684,7 +13726,7 @@
       <c r="U16" t="s">
         <v>87</v>
       </c>
-      <c r="V16" s="6">
+      <c r="V16">
         <v>1</v>
       </c>
       <c r="W16" t="s">
@@ -13908,7 +13950,7 @@
       <c r="U17" t="s">
         <v>87</v>
       </c>
-      <c r="V17" s="6">
+      <c r="V17">
         <v>1</v>
       </c>
       <c r="W17" t="s">
@@ -14132,7 +14174,7 @@
       <c r="U18" t="s">
         <v>95</v>
       </c>
-      <c r="V18" s="6">
+      <c r="V18">
         <v>1</v>
       </c>
       <c r="W18" t="s">
@@ -14356,7 +14398,7 @@
       <c r="U19" t="s">
         <v>87</v>
       </c>
-      <c r="V19" s="6">
+      <c r="V19">
         <v>1</v>
       </c>
       <c r="W19" t="s">
@@ -14580,7 +14622,7 @@
       <c r="U20" t="s">
         <v>95</v>
       </c>
-      <c r="V20" s="6">
+      <c r="V20">
         <v>1</v>
       </c>
       <c r="W20" t="s">
@@ -14804,7 +14846,7 @@
       <c r="U21" t="s">
         <v>98</v>
       </c>
-      <c r="V21" s="6">
+      <c r="V21">
         <v>1</v>
       </c>
       <c r="W21" t="s">
@@ -15028,7 +15070,7 @@
       <c r="U22" t="s">
         <v>87</v>
       </c>
-      <c r="V22" s="6">
+      <c r="V22">
         <v>1</v>
       </c>
       <c r="W22" t="s">
@@ -15252,7 +15294,7 @@
       <c r="U23" t="s">
         <v>98</v>
       </c>
-      <c r="V23" s="6">
+      <c r="V23">
         <v>1</v>
       </c>
       <c r="W23" t="s">
@@ -15476,7 +15518,7 @@
       <c r="U24" t="s">
         <v>87</v>
       </c>
-      <c r="V24" s="6">
+      <c r="V24">
         <v>1</v>
       </c>
       <c r="W24" t="s">
@@ -15700,7 +15742,7 @@
       <c r="U25" t="s">
         <v>98</v>
       </c>
-      <c r="V25" s="6">
+      <c r="V25">
         <v>1</v>
       </c>
       <c r="W25" t="s">
@@ -15924,7 +15966,7 @@
       <c r="U26" t="s">
         <v>98</v>
       </c>
-      <c r="V26" s="6">
+      <c r="V26">
         <v>1</v>
       </c>
       <c r="W26" t="s">
@@ -16148,7 +16190,7 @@
       <c r="U27" t="s">
         <v>95</v>
       </c>
-      <c r="V27" s="6">
+      <c r="V27">
         <v>1</v>
       </c>
       <c r="W27" t="s">
@@ -16372,7 +16414,7 @@
       <c r="U28" t="s">
         <v>95</v>
       </c>
-      <c r="V28" s="6">
+      <c r="V28">
         <v>1</v>
       </c>
       <c r="W28" t="s">
@@ -16596,7 +16638,7 @@
       <c r="U29" t="s">
         <v>98</v>
       </c>
-      <c r="V29" s="6">
+      <c r="V29">
         <v>1</v>
       </c>
       <c r="W29" t="s">
@@ -16820,7 +16862,7 @@
       <c r="U30" t="s">
         <v>87</v>
       </c>
-      <c r="V30" s="6">
+      <c r="V30">
         <v>1</v>
       </c>
       <c r="W30" t="s">
@@ -17044,7 +17086,7 @@
       <c r="U31" t="s">
         <v>87</v>
       </c>
-      <c r="V31" s="6">
+      <c r="V31">
         <v>1</v>
       </c>
       <c r="W31" t="s">
@@ -17268,7 +17310,7 @@
       <c r="U32" t="s">
         <v>87</v>
       </c>
-      <c r="V32" s="6">
+      <c r="V32">
         <v>1</v>
       </c>
       <c r="W32" t="s">
@@ -17492,7 +17534,7 @@
       <c r="U33" t="s">
         <v>95</v>
       </c>
-      <c r="V33" s="6">
+      <c r="V33">
         <v>1</v>
       </c>
       <c r="W33" t="s">
@@ -17716,7 +17758,7 @@
       <c r="U34" t="s">
         <v>98</v>
       </c>
-      <c r="V34" s="6">
+      <c r="V34">
         <v>1</v>
       </c>
       <c r="W34" t="s">
@@ -17940,7 +17982,7 @@
       <c r="U35" t="s">
         <v>87</v>
       </c>
-      <c r="V35" s="6">
+      <c r="V35">
         <v>1</v>
       </c>
       <c r="W35" t="s">
@@ -18164,7 +18206,7 @@
       <c r="U36" t="s">
         <v>98</v>
       </c>
-      <c r="V36" s="6">
+      <c r="V36">
         <v>1</v>
       </c>
       <c r="W36" t="s">
@@ -18388,7 +18430,7 @@
       <c r="U37" t="s">
         <v>87</v>
       </c>
-      <c r="V37" s="6">
+      <c r="V37">
         <v>1</v>
       </c>
       <c r="W37" t="s">
@@ -18612,7 +18654,7 @@
       <c r="U38" t="s">
         <v>95</v>
       </c>
-      <c r="V38" s="6">
+      <c r="V38">
         <v>1</v>
       </c>
       <c r="W38" t="s">
@@ -18836,7 +18878,7 @@
       <c r="U39" t="s">
         <v>98</v>
       </c>
-      <c r="V39" s="6">
+      <c r="V39">
         <v>1</v>
       </c>
       <c r="W39" t="s">
@@ -19060,7 +19102,7 @@
       <c r="U40" t="s">
         <v>95</v>
       </c>
-      <c r="V40" s="6">
+      <c r="V40">
         <v>1</v>
       </c>
       <c r="W40" t="s">
@@ -19284,7 +19326,7 @@
       <c r="U41" t="s">
         <v>95</v>
       </c>
-      <c r="V41" s="6">
+      <c r="V41">
         <v>1</v>
       </c>
       <c r="W41" t="s">
@@ -19508,7 +19550,7 @@
       <c r="U42" t="s">
         <v>87</v>
       </c>
-      <c r="V42" s="6">
+      <c r="V42">
         <v>1</v>
       </c>
       <c r="W42" t="s">
@@ -19732,7 +19774,7 @@
       <c r="U43" t="s">
         <v>87</v>
       </c>
-      <c r="V43" s="6">
+      <c r="V43">
         <v>1</v>
       </c>
       <c r="W43" t="s">
@@ -19956,7 +19998,7 @@
       <c r="U44" t="s">
         <v>95</v>
       </c>
-      <c r="V44" s="6">
+      <c r="V44">
         <v>1</v>
       </c>
       <c r="W44" t="s">
@@ -20180,7 +20222,7 @@
       <c r="U45" t="s">
         <v>87</v>
       </c>
-      <c r="V45" s="6">
+      <c r="V45">
         <v>1</v>
       </c>
       <c r="W45" t="s">
@@ -20404,7 +20446,7 @@
       <c r="U46" t="s">
         <v>95</v>
       </c>
-      <c r="V46" s="6">
+      <c r="V46">
         <v>1</v>
       </c>
       <c r="W46" t="s">
@@ -20628,7 +20670,7 @@
       <c r="U47" t="s">
         <v>95</v>
       </c>
-      <c r="V47" s="6">
+      <c r="V47">
         <v>1</v>
       </c>
       <c r="W47" t="s">
@@ -20852,7 +20894,7 @@
       <c r="U48" t="s">
         <v>98</v>
       </c>
-      <c r="V48" s="6">
+      <c r="V48">
         <v>1</v>
       </c>
       <c r="W48" t="s">
@@ -21076,7 +21118,7 @@
       <c r="U49" t="s">
         <v>87</v>
       </c>
-      <c r="V49" s="6">
+      <c r="V49">
         <v>1</v>
       </c>
       <c r="W49" t="s">
@@ -21300,7 +21342,7 @@
       <c r="U50" t="s">
         <v>98</v>
       </c>
-      <c r="V50" s="6">
+      <c r="V50">
         <v>1</v>
       </c>
       <c r="W50" t="s">
@@ -21524,7 +21566,7 @@
       <c r="U51" t="s">
         <v>95</v>
       </c>
-      <c r="V51" s="6">
+      <c r="V51">
         <v>2</v>
       </c>
       <c r="W51" t="s">
@@ -21748,7 +21790,7 @@
       <c r="U52" t="s">
         <v>98</v>
       </c>
-      <c r="V52" s="6">
+      <c r="V52">
         <v>1</v>
       </c>
       <c r="W52" t="s">
@@ -21972,7 +22014,7 @@
       <c r="U53" t="s">
         <v>87</v>
       </c>
-      <c r="V53" s="6">
+      <c r="V53">
         <v>2</v>
       </c>
       <c r="W53" t="s">
@@ -22196,7 +22238,7 @@
       <c r="U54" t="s">
         <v>95</v>
       </c>
-      <c r="V54" s="6">
+      <c r="V54">
         <v>2</v>
       </c>
       <c r="W54" t="s">
@@ -22420,7 +22462,7 @@
       <c r="U55" t="s">
         <v>98</v>
       </c>
-      <c r="V55" s="6">
+      <c r="V55">
         <v>1</v>
       </c>
       <c r="W55" t="s">
@@ -22644,7 +22686,7 @@
       <c r="U56" t="s">
         <v>87</v>
       </c>
-      <c r="V56" s="6">
+      <c r="V56">
         <v>2</v>
       </c>
       <c r="W56" t="s">
@@ -22868,7 +22910,7 @@
       <c r="U57" t="s">
         <v>95</v>
       </c>
-      <c r="V57" s="6">
+      <c r="V57">
         <v>2</v>
       </c>
       <c r="W57" t="s">
@@ -23092,7 +23134,7 @@
       <c r="U58" t="s">
         <v>98</v>
       </c>
-      <c r="V58" s="6">
+      <c r="V58">
         <v>2</v>
       </c>
       <c r="W58" t="s">
@@ -23316,7 +23358,7 @@
       <c r="U59" t="s">
         <v>87</v>
       </c>
-      <c r="V59" s="6">
+      <c r="V59">
         <v>2</v>
       </c>
       <c r="W59" t="s">
@@ -23540,7 +23582,7 @@
       <c r="U60" t="s">
         <v>95</v>
       </c>
-      <c r="V60" s="6">
+      <c r="V60">
         <v>2</v>
       </c>
       <c r="W60" t="s">
@@ -23764,7 +23806,7 @@
       <c r="U61" t="s">
         <v>98</v>
       </c>
-      <c r="V61" s="6">
+      <c r="V61">
         <v>2</v>
       </c>
       <c r="W61" t="s">
@@ -23988,7 +24030,7 @@
       <c r="U62" t="s">
         <v>87</v>
       </c>
-      <c r="V62" s="6">
+      <c r="V62">
         <v>2</v>
       </c>
       <c r="W62" t="s">
@@ -24212,7 +24254,7 @@
       <c r="U63" t="s">
         <v>95</v>
       </c>
-      <c r="V63" s="6">
+      <c r="V63">
         <v>2</v>
       </c>
       <c r="W63" t="s">
@@ -24436,7 +24478,7 @@
       <c r="U64" t="s">
         <v>98</v>
       </c>
-      <c r="V64" s="6">
+      <c r="V64">
         <v>2</v>
       </c>
       <c r="W64" t="s">
@@ -24660,7 +24702,7 @@
       <c r="U65" t="s">
         <v>87</v>
       </c>
-      <c r="V65" s="6">
+      <c r="V65">
         <v>2</v>
       </c>
       <c r="W65" t="s">
@@ -24884,7 +24926,7 @@
       <c r="U66" t="s">
         <v>95</v>
       </c>
-      <c r="V66" s="6">
+      <c r="V66">
         <v>2</v>
       </c>
       <c r="W66" t="s">
@@ -25108,7 +25150,7 @@
       <c r="U67" t="s">
         <v>98</v>
       </c>
-      <c r="V67" s="6">
+      <c r="V67">
         <v>2</v>
       </c>
       <c r="W67" t="s">
@@ -25332,7 +25374,7 @@
       <c r="U68" t="s">
         <v>87</v>
       </c>
-      <c r="V68" s="6">
+      <c r="V68">
         <v>2</v>
       </c>
       <c r="W68" t="s">
@@ -25556,7 +25598,7 @@
       <c r="U69" t="s">
         <v>95</v>
       </c>
-      <c r="V69" s="6">
+      <c r="V69">
         <v>2</v>
       </c>
       <c r="W69" t="s">
@@ -25780,7 +25822,7 @@
       <c r="U70" t="s">
         <v>87</v>
       </c>
-      <c r="V70" s="6">
+      <c r="V70">
         <v>2</v>
       </c>
       <c r="W70" t="s">
@@ -26004,7 +26046,7 @@
       <c r="U71" t="s">
         <v>98</v>
       </c>
-      <c r="V71" s="6">
+      <c r="V71">
         <v>2</v>
       </c>
       <c r="W71" t="s">
@@ -26228,7 +26270,7 @@
       <c r="U72" t="s">
         <v>95</v>
       </c>
-      <c r="V72" s="6">
+      <c r="V72">
         <v>2</v>
       </c>
       <c r="W72" t="s">
@@ -26452,7 +26494,7 @@
       <c r="U73" t="s">
         <v>87</v>
       </c>
-      <c r="V73" s="6">
+      <c r="V73">
         <v>2</v>
       </c>
       <c r="W73" t="s">
@@ -26676,7 +26718,7 @@
       <c r="U74" t="s">
         <v>98</v>
       </c>
-      <c r="V74" s="6">
+      <c r="V74">
         <v>2</v>
       </c>
       <c r="W74" t="s">
@@ -26900,7 +26942,7 @@
       <c r="U75" t="s">
         <v>95</v>
       </c>
-      <c r="V75" s="6">
+      <c r="V75">
         <v>2</v>
       </c>
       <c r="W75" t="s">
@@ -27124,7 +27166,7 @@
       <c r="U76" t="s">
         <v>87</v>
       </c>
-      <c r="V76" s="6">
+      <c r="V76">
         <v>2</v>
       </c>
       <c r="W76" t="s">
@@ -27348,7 +27390,7 @@
       <c r="U77" t="s">
         <v>98</v>
       </c>
-      <c r="V77" s="6">
+      <c r="V77">
         <v>2</v>
       </c>
       <c r="W77" t="s">
@@ -27572,7 +27614,7 @@
       <c r="U78" t="s">
         <v>95</v>
       </c>
-      <c r="V78" s="6">
+      <c r="V78">
         <v>2</v>
       </c>
       <c r="W78" t="s">
@@ -27796,7 +27838,7 @@
       <c r="U79" t="s">
         <v>87</v>
       </c>
-      <c r="V79" s="6">
+      <c r="V79">
         <v>2</v>
       </c>
       <c r="W79" t="s">
@@ -28020,7 +28062,7 @@
       <c r="U80" t="s">
         <v>98</v>
       </c>
-      <c r="V80" s="6">
+      <c r="V80">
         <v>2</v>
       </c>
       <c r="W80" t="s">
@@ -28244,7 +28286,7 @@
       <c r="U81" t="s">
         <v>95</v>
       </c>
-      <c r="V81" s="6">
+      <c r="V81">
         <v>2</v>
       </c>
       <c r="W81" t="s">
@@ -28468,7 +28510,7 @@
       <c r="U82" t="s">
         <v>87</v>
       </c>
-      <c r="V82" s="6">
+      <c r="V82">
         <v>2</v>
       </c>
       <c r="W82" t="s">
@@ -28692,7 +28734,7 @@
       <c r="U83" t="s">
         <v>95</v>
       </c>
-      <c r="V83" s="6">
+      <c r="V83">
         <v>2</v>
       </c>
       <c r="W83" t="s">
@@ -28916,7 +28958,7 @@
       <c r="U84" t="s">
         <v>98</v>
       </c>
-      <c r="V84" s="6">
+      <c r="V84">
         <v>2</v>
       </c>
       <c r="W84" t="s">
@@ -29140,7 +29182,7 @@
       <c r="U85" t="s">
         <v>87</v>
       </c>
-      <c r="V85" s="6">
+      <c r="V85">
         <v>2</v>
       </c>
       <c r="W85" t="s">
@@ -29364,7 +29406,7 @@
       <c r="U86" t="s">
         <v>95</v>
       </c>
-      <c r="V86" s="6">
+      <c r="V86">
         <v>2</v>
       </c>
       <c r="W86" t="s">
@@ -29588,7 +29630,7 @@
       <c r="U87" t="s">
         <v>98</v>
       </c>
-      <c r="V87" s="6">
+      <c r="V87">
         <v>2</v>
       </c>
       <c r="W87" t="s">
@@ -29812,7 +29854,7 @@
       <c r="U88" t="s">
         <v>87</v>
       </c>
-      <c r="V88" s="6">
+      <c r="V88">
         <v>2</v>
       </c>
       <c r="W88" t="s">
@@ -30036,7 +30078,7 @@
       <c r="U89" t="s">
         <v>95</v>
       </c>
-      <c r="V89" s="6">
+      <c r="V89">
         <v>2</v>
       </c>
       <c r="W89" t="s">
@@ -30260,7 +30302,7 @@
       <c r="U90" t="s">
         <v>98</v>
       </c>
-      <c r="V90" s="6">
+      <c r="V90">
         <v>2</v>
       </c>
       <c r="W90" t="s">
@@ -30484,7 +30526,7 @@
       <c r="U91" t="s">
         <v>87</v>
       </c>
-      <c r="V91" s="6">
+      <c r="V91">
         <v>2</v>
       </c>
       <c r="W91" t="s">
@@ -30708,7 +30750,7 @@
       <c r="U92" t="s">
         <v>95</v>
       </c>
-      <c r="V92" s="6">
+      <c r="V92">
         <v>2</v>
       </c>
       <c r="W92" t="s">
@@ -30932,7 +30974,7 @@
       <c r="U93" t="s">
         <v>98</v>
       </c>
-      <c r="V93" s="6">
+      <c r="V93">
         <v>2</v>
       </c>
       <c r="W93" t="s">
@@ -31156,7 +31198,7 @@
       <c r="U94" t="s">
         <v>87</v>
       </c>
-      <c r="V94" s="6">
+      <c r="V94">
         <v>2</v>
       </c>
       <c r="W94" t="s">
@@ -31380,7 +31422,7 @@
       <c r="U95" t="s">
         <v>95</v>
       </c>
-      <c r="V95" s="6">
+      <c r="V95">
         <v>2</v>
       </c>
       <c r="W95" t="s">
@@ -31604,7 +31646,7 @@
       <c r="U96" t="s">
         <v>98</v>
       </c>
-      <c r="V96" s="6">
+      <c r="V96">
         <v>2</v>
       </c>
       <c r="W96" t="s">
@@ -31828,7 +31870,7 @@
       <c r="U97" t="s">
         <v>87</v>
       </c>
-      <c r="V97" s="6">
+      <c r="V97">
         <v>2</v>
       </c>
       <c r="W97" t="s">
@@ -32052,7 +32094,7 @@
       <c r="U98" t="s">
         <v>95</v>
       </c>
-      <c r="V98" s="6">
+      <c r="V98">
         <v>2</v>
       </c>
       <c r="W98" t="s">
@@ -32276,7 +32318,7 @@
       <c r="U99" t="s">
         <v>98</v>
       </c>
-      <c r="V99" s="6">
+      <c r="V99">
         <v>2</v>
       </c>
       <c r="W99" t="s">
@@ -32500,7 +32542,7 @@
       <c r="U100" t="s">
         <v>87</v>
       </c>
-      <c r="V100" s="6">
+      <c r="V100">
         <v>2</v>
       </c>
       <c r="W100" t="s">
@@ -32724,7 +32766,7 @@
       <c r="U101" t="s">
         <v>95</v>
       </c>
-      <c r="V101" s="6">
+      <c r="V101">
         <v>2</v>
       </c>
       <c r="W101" t="s">
@@ -32948,7 +32990,7 @@
       <c r="U102" t="s">
         <v>87</v>
       </c>
-      <c r="V102" s="6">
+      <c r="V102">
         <v>2</v>
       </c>
       <c r="W102" t="s">
@@ -33172,7 +33214,7 @@
       <c r="U103" t="s">
         <v>98</v>
       </c>
-      <c r="V103" s="6">
+      <c r="V103">
         <v>2</v>
       </c>
       <c r="W103" t="s">
@@ -33396,7 +33438,7 @@
       <c r="U104" t="s">
         <v>95</v>
       </c>
-      <c r="V104" s="6">
+      <c r="V104">
         <v>1</v>
       </c>
       <c r="W104" t="s">
@@ -33620,7 +33662,7 @@
       <c r="U105" t="s">
         <v>98</v>
       </c>
-      <c r="V105" s="6">
+      <c r="V105">
         <v>2</v>
       </c>
       <c r="W105" t="s">
@@ -33844,7 +33886,7 @@
       <c r="U106" t="s">
         <v>95</v>
       </c>
-      <c r="V106" s="6">
+      <c r="V106">
         <v>1</v>
       </c>
       <c r="W106" t="s">
@@ -34068,7 +34110,7 @@
       <c r="U107" t="s">
         <v>98</v>
       </c>
-      <c r="V107" s="6">
+      <c r="V107">
         <v>2</v>
       </c>
       <c r="W107" t="s">
@@ -34292,7 +34334,7 @@
       <c r="U108" t="s">
         <v>98</v>
       </c>
-      <c r="V108" s="6">
+      <c r="V108">
         <v>2</v>
       </c>
       <c r="W108" t="s">
@@ -34516,7 +34558,7 @@
       <c r="U109" t="s">
         <v>87</v>
       </c>
-      <c r="V109" s="6">
+      <c r="V109">
         <v>1</v>
       </c>
       <c r="W109" t="s">
@@ -34686,21 +34728,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2999E7B8-524B-4164-A89A-1339340538A3}">
-  <dimension ref="A3:L49"/>
+  <dimension ref="A3:L64"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="40.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="40" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="36.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="37" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="41.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="41" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="37" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="38" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="52.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="51.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="46.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="47.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="54" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="53.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="47.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="49.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
@@ -34743,1749 +34785,2319 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B4" s="6">
-        <v>0.51215546138866819</v>
-      </c>
-      <c r="C4" s="6">
-        <v>1.5174960648004228E-2</v>
-      </c>
-      <c r="D4" s="6">
-        <v>0.3251821284102524</v>
-      </c>
-      <c r="E4" s="6">
-        <v>0.61823705912657967</v>
-      </c>
-      <c r="F4" s="6">
-        <v>0.61723692331875346</v>
-      </c>
-      <c r="G4" s="6">
-        <v>0.32218267608475332</v>
-      </c>
-      <c r="H4" s="6">
-        <v>-0.1349532885580968</v>
-      </c>
-      <c r="I4" s="6">
-        <v>0.12877205554650131</v>
-      </c>
-      <c r="J4" s="6">
-        <v>0.17878959773818201</v>
-      </c>
-      <c r="K4" s="6">
-        <v>-7.0812253023324542E-2</v>
-      </c>
-      <c r="L4" s="6">
-        <v>36</v>
+        <v>115</v>
+      </c>
+      <c r="B4" s="7">
+        <v>0.46177620168664874</v>
+      </c>
+      <c r="C4" s="7">
+        <v>8.1703844425733474E-2</v>
+      </c>
+      <c r="D4" s="7">
+        <v>0.32987317903990498</v>
+      </c>
+      <c r="E4" s="7">
+        <v>0.58319919431365752</v>
+      </c>
+      <c r="F4" s="7">
+        <v>0.54069872865810031</v>
+      </c>
+      <c r="G4" s="7">
+        <v>0.27458684216628015</v>
+      </c>
+      <c r="H4" s="7">
+        <v>-6.2638460871008356E-2</v>
+      </c>
+      <c r="I4" s="7">
+        <v>0.19216350756692341</v>
+      </c>
+      <c r="J4" s="7">
+        <v>0.26732007150245446</v>
+      </c>
+      <c r="K4" s="7">
+        <v>-3.3689014722435996E-2</v>
+      </c>
+      <c r="L4" s="7">
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="5">
-        <v>1</v>
-      </c>
-      <c r="B5" s="6">
-        <v>0.55716082219162189</v>
-      </c>
-      <c r="C5" s="6">
-        <v>-7.4529068056838427E-2</v>
-      </c>
-      <c r="D5" s="6">
-        <v>0.32730732242516625</v>
-      </c>
-      <c r="E5" s="6">
-        <v>0.62476606642070065</v>
-      </c>
-      <c r="F5" s="6">
-        <v>0.64901958016856054</v>
-      </c>
-      <c r="G5" s="6">
-        <v>0.45494564383387659</v>
-      </c>
-      <c r="H5" s="6">
-        <v>-0.27031947170731452</v>
-      </c>
-      <c r="I5" s="6">
-        <v>5.2404503445270742E-2</v>
-      </c>
-      <c r="J5" s="6">
-        <v>0.11177253523948176</v>
-      </c>
-      <c r="K5" s="6">
-        <v>-0.14619953463755322</v>
-      </c>
-      <c r="L5" s="6">
-        <v>18</v>
+      <c r="A5" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B5" s="7">
+        <v>0.45964326916962389</v>
+      </c>
+      <c r="C5" s="7">
+        <v>6.8427507682051426E-3</v>
+      </c>
+      <c r="D5" s="7">
+        <v>0.32544213066271982</v>
+      </c>
+      <c r="E5" s="7">
+        <v>0.56213362638878561</v>
+      </c>
+      <c r="F5" s="7">
+        <v>0.52959750737176947</v>
+      </c>
+      <c r="G5" s="7">
+        <v>0.20219239877359663</v>
+      </c>
+      <c r="H5" s="7">
+        <v>-0.25051851320945712</v>
+      </c>
+      <c r="I5" s="7">
+        <v>0.1265704154470515</v>
+      </c>
+      <c r="J5" s="7">
+        <v>0.23026309780627244</v>
+      </c>
+      <c r="K5" s="7">
+        <v>-7.3452719772600941E-2</v>
+      </c>
+      <c r="L5" s="7">
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="B6" s="6">
+      <c r="A6" s="6">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
         <v>0.47763971194166399</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="7">
         <v>-0.14103495545202385</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="7">
         <v>0.4479057640249347</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="7">
         <v>0.51671616358919759</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="7">
         <v>0.44760684316787808</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="7">
         <v>0.26074441182530922</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="7">
         <v>-0.5206955142779971</v>
       </c>
-      <c r="I6" s="6">
+      <c r="I6" s="7">
         <v>3.2225377734906892E-2</v>
       </c>
-      <c r="J6" s="6">
+      <c r="J6" s="7">
         <v>0.17334175636222626</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="7">
         <v>-0.18997336171507009</v>
       </c>
-      <c r="L6" s="6">
+      <c r="L6" s="7">
         <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="B7" s="6">
-        <v>0.4512388495357666</v>
-      </c>
-      <c r="C7" s="6">
-        <v>-0.20266186830233138</v>
-      </c>
-      <c r="D7" s="6">
-        <v>0.71863391825093703</v>
-      </c>
-      <c r="E7" s="6">
-        <v>0.20159886267361371</v>
-      </c>
-      <c r="F7" s="6">
-        <v>0.39149405268912085</v>
-      </c>
-      <c r="G7" s="6">
-        <v>0.29642664155419723</v>
-      </c>
-      <c r="H7" s="6">
-        <v>-0.35260695488708094</v>
-      </c>
-      <c r="I7" s="6">
-        <v>-0.14011598334413874</v>
-      </c>
-      <c r="J7" s="6">
-        <v>-0.10482193106263639</v>
-      </c>
-      <c r="K7" s="6">
-        <v>-9.2506504015408428E-2</v>
-      </c>
-      <c r="L7" s="6">
+      <c r="A7" s="6">
+        <v>2</v>
+      </c>
+      <c r="B7" s="7">
+        <v>0.44164682639758368</v>
+      </c>
+      <c r="C7" s="7">
+        <v>0.15472045698843415</v>
+      </c>
+      <c r="D7" s="7">
+        <v>0.20297849730050502</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0.60755108918837375</v>
+      </c>
+      <c r="F7" s="7">
+        <v>0.61158817157566081</v>
+      </c>
+      <c r="G7" s="7">
+        <v>0.14364038572188401</v>
+      </c>
+      <c r="H7" s="7">
+        <v>1.9658487859082873E-2</v>
+      </c>
+      <c r="I7" s="7">
+        <v>0.22091545315919611</v>
+      </c>
+      <c r="J7" s="7">
+        <v>0.28718443925031861</v>
+      </c>
+      <c r="K7" s="7">
+        <v>4.3067922169868211E-2</v>
+      </c>
+      <c r="L7" s="7">
         <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="B8" s="6">
-        <v>0.66383684707962776</v>
-      </c>
-      <c r="C8" s="6">
-        <v>0.37834114749734399</v>
-      </c>
-      <c r="D8" s="6">
-        <v>2.2601947846949532E-2</v>
-      </c>
-      <c r="E8" s="6">
-        <v>0.94504021713807151</v>
-      </c>
-      <c r="F8" s="6">
-        <v>0.87720825907510669</v>
-      </c>
-      <c r="G8" s="6">
-        <v>0.82403046446928219</v>
-      </c>
-      <c r="H8" s="6">
-        <v>-1.1405430870144969E-2</v>
-      </c>
-      <c r="I8" s="6">
-        <v>0.70374208051345255</v>
-      </c>
-      <c r="J8" s="6">
-        <v>0.43096841154740506</v>
-      </c>
-      <c r="K8" s="6">
-        <v>0.354794640388639</v>
-      </c>
-      <c r="L8" s="6">
-        <v>3</v>
+      <c r="A8" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B8" s="7">
+        <v>0.4357140813280882</v>
+      </c>
+      <c r="C8" s="7">
+        <v>0.14522396979995519</v>
+      </c>
+      <c r="D8" s="7">
+        <v>0.31263728151572884</v>
+      </c>
+      <c r="E8" s="7">
+        <v>0.58365015004086052</v>
+      </c>
+      <c r="F8" s="7">
+        <v>0.51887368172368642</v>
+      </c>
+      <c r="G8" s="7">
+        <v>0.26962949447142964</v>
+      </c>
+      <c r="H8" s="7">
+        <v>7.1856588869452301E-2</v>
+      </c>
+      <c r="I8" s="7">
+        <v>0.27528705153845251</v>
+      </c>
+      <c r="J8" s="7">
+        <v>0.28387186485930965</v>
+      </c>
+      <c r="K8" s="7">
+        <v>-4.7039596198043066E-3</v>
+      </c>
+      <c r="L8" s="7">
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="B9" s="6">
-        <v>0.62554062294746215</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-0.79447121757044137</v>
-      </c>
-      <c r="D9" s="6">
-        <v>0.32166504623880082</v>
-      </c>
-      <c r="E9" s="6">
-        <v>0.56754186514173732</v>
-      </c>
-      <c r="F9" s="6">
-        <v>0.56018437165061152</v>
-      </c>
-      <c r="G9" s="6">
-        <v>0.54269609656372542</v>
-      </c>
-      <c r="H9" s="6">
-        <v>-0.4372745883965094</v>
-      </c>
-      <c r="I9" s="6">
-        <v>-0.93883827720979485</v>
-      </c>
-      <c r="J9" s="6">
-        <v>-0.64907580322306002</v>
-      </c>
-      <c r="K9" s="6">
-        <v>-0.76005381893694857</v>
-      </c>
-      <c r="L9" s="6">
+      <c r="A9" s="6">
+        <v>1</v>
+      </c>
+      <c r="B9" s="7">
+        <v>0.51317131096266033</v>
+      </c>
+      <c r="C9" s="7">
+        <v>0.32132886892025753</v>
+      </c>
+      <c r="D9" s="7">
+        <v>0.33994010061038415</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.72784003508917927</v>
+      </c>
+      <c r="F9" s="7">
+        <v>0.60923846574490925</v>
+      </c>
+      <c r="G9" s="7">
+        <v>0.41791020802472856</v>
+      </c>
+      <c r="H9" s="7">
+        <v>0.1051133452605461</v>
+      </c>
+      <c r="I9" s="7">
+        <v>0.6225606650600789</v>
+      </c>
+      <c r="J9" s="7">
+        <v>0.56202121591119469</v>
+      </c>
+      <c r="K9" s="7">
+        <v>3.4839889959073674E-2</v>
+      </c>
+      <c r="L9" s="7">
         <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="B10" s="6">
-        <v>0.6138157437778643</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-3.4862205004359361E-3</v>
-      </c>
-      <c r="D10" s="6">
-        <v>0.16922130705442448</v>
-      </c>
-      <c r="E10" s="6">
-        <v>0.81835098263436146</v>
-      </c>
-      <c r="F10" s="6">
-        <v>0.78534528081842669</v>
-      </c>
-      <c r="G10" s="6">
-        <v>0.63761387382735257</v>
-      </c>
-      <c r="H10" s="6">
-        <v>-2.3778768328583045E-2</v>
-      </c>
-      <c r="I10" s="6">
-        <v>-3.2207113447426022E-2</v>
-      </c>
-      <c r="J10" s="6">
-        <v>1.1624500593604351E-2</v>
-      </c>
-      <c r="K10" s="6">
-        <v>-0.21691001356242637</v>
-      </c>
-      <c r="L10" s="6">
+      <c r="A10" s="6">
+        <v>2</v>
+      </c>
+      <c r="B10" s="7">
+        <v>0.35825685169351607</v>
+      </c>
+      <c r="C10" s="7">
+        <v>-3.0880929320347097E-2</v>
+      </c>
+      <c r="D10" s="7">
+        <v>0.28533446242107346</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.43946026499254165</v>
+      </c>
+      <c r="F10" s="7">
+        <v>0.42850889770246364</v>
+      </c>
+      <c r="G10" s="7">
+        <v>0.12134878091813073</v>
+      </c>
+      <c r="H10" s="7">
+        <v>3.859983247835852E-2</v>
+      </c>
+      <c r="I10" s="7">
+        <v>-7.1986561983173811E-2</v>
+      </c>
+      <c r="J10" s="7">
+        <v>5.7225138074246951E-3</v>
+      </c>
+      <c r="K10" s="7">
+        <v>-4.4247809198682285E-2</v>
+      </c>
+      <c r="L10" s="7">
         <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="B11" s="6">
-        <v>0.51089315786734568</v>
-      </c>
-      <c r="C11" s="6">
-        <v>0.31613870598685806</v>
-      </c>
-      <c r="D11" s="6">
-        <v>0.28381595113495078</v>
-      </c>
-      <c r="E11" s="6">
-        <v>0.69934830734722297</v>
-      </c>
-      <c r="F11" s="6">
-        <v>0.83227867361021912</v>
-      </c>
-      <c r="G11" s="6">
-        <v>0.16816237476339291</v>
-      </c>
-      <c r="H11" s="6">
-        <v>-0.27615557348357217</v>
-      </c>
-      <c r="I11" s="6">
-        <v>0.68962093642462452</v>
-      </c>
-      <c r="J11" s="6">
-        <v>0.8085982772193514</v>
-      </c>
-      <c r="K11" s="6">
-        <v>2.7451850015895157E-2</v>
-      </c>
-      <c r="L11" s="6">
-        <v>3</v>
+      <c r="A11" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B11" s="7">
+        <v>0.48997125456223412</v>
+      </c>
+      <c r="C11" s="7">
+        <v>9.304481270904004E-2</v>
+      </c>
+      <c r="D11" s="7">
+        <v>0.35154012494126619</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0.60381380651132632</v>
+      </c>
+      <c r="F11" s="7">
+        <v>0.57362499687884505</v>
+      </c>
+      <c r="G11" s="7">
+        <v>0.35193863325381419</v>
+      </c>
+      <c r="H11" s="7">
+        <v>-9.2534582730202774E-3</v>
+      </c>
+      <c r="I11" s="7">
+        <v>0.17463305571526619</v>
+      </c>
+      <c r="J11" s="7">
+        <v>0.28782525184178132</v>
+      </c>
+      <c r="K11" s="7">
+        <v>-2.2910364774902752E-2</v>
+      </c>
+      <c r="L11" s="7">
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="5">
-        <v>2</v>
-      </c>
-      <c r="B12" s="6">
-        <v>0.46715010058571454</v>
-      </c>
-      <c r="C12" s="6">
-        <v>0.10487898935284687</v>
-      </c>
-      <c r="D12" s="6">
-        <v>0.32305693439533861</v>
-      </c>
-      <c r="E12" s="6">
-        <v>0.61170805183245891</v>
-      </c>
-      <c r="F12" s="6">
-        <v>0.5854542664689466</v>
-      </c>
-      <c r="G12" s="6">
-        <v>0.18941970833563004</v>
-      </c>
-      <c r="H12" s="6">
-        <v>4.1289459112097478E-4</v>
-      </c>
-      <c r="I12" s="6">
-        <v>0.20513960764773184</v>
-      </c>
-      <c r="J12" s="6">
-        <v>0.24580666023688233</v>
-      </c>
-      <c r="K12" s="6">
-        <v>4.5750285909041443E-3</v>
-      </c>
-      <c r="L12" s="6">
-        <v>18</v>
+      <c r="A12" s="6">
+        <v>1</v>
+      </c>
+      <c r="B12" s="7">
+        <v>0.58733400631313504</v>
+      </c>
+      <c r="C12" s="7">
+        <v>0.26916136399111029</v>
+      </c>
+      <c r="D12" s="7">
+        <v>0.45343303929977302</v>
+      </c>
+      <c r="E12" s="7">
+        <v>0.73083718727239122</v>
+      </c>
+      <c r="F12" s="7">
+        <v>0.6601773280567671</v>
+      </c>
+      <c r="G12" s="7">
+        <v>0.48433036883308223</v>
+      </c>
+      <c r="H12" s="7">
+        <v>3.6782046125197303E-2</v>
+      </c>
+      <c r="I12" s="7">
+        <v>0.4642192086577599</v>
+      </c>
+      <c r="J12" s="7">
+        <v>0.553134785453401</v>
+      </c>
+      <c r="K12" s="7">
+        <v>5.5841510110270137E-2</v>
+      </c>
+      <c r="L12" s="7">
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="B13" s="6">
-        <v>0.44164682639758368</v>
-      </c>
-      <c r="C13" s="6">
-        <v>0.15472045698843415</v>
-      </c>
-      <c r="D13" s="6">
-        <v>0.20297849730050502</v>
-      </c>
-      <c r="E13" s="6">
-        <v>0.60755108918837375</v>
-      </c>
-      <c r="F13" s="6">
-        <v>0.61158817157566081</v>
-      </c>
-      <c r="G13" s="6">
-        <v>0.14364038572188401</v>
-      </c>
-      <c r="H13" s="6">
-        <v>1.9658487859082873E-2</v>
-      </c>
-      <c r="I13" s="6">
-        <v>0.22091545315919611</v>
-      </c>
-      <c r="J13" s="6">
-        <v>0.28718443925031861</v>
-      </c>
-      <c r="K13" s="6">
-        <v>4.3067922169868211E-2</v>
-      </c>
-      <c r="L13" s="6">
+      <c r="A13" s="6">
+        <v>2</v>
+      </c>
+      <c r="B13" s="7">
+        <v>0.39260850281133325</v>
+      </c>
+      <c r="C13" s="7">
+        <v>-8.3071738573030227E-2</v>
+      </c>
+      <c r="D13" s="7">
+        <v>0.24964721058275932</v>
+      </c>
+      <c r="E13" s="7">
+        <v>0.47679042575026126</v>
+      </c>
+      <c r="F13" s="7">
+        <v>0.48707266570092295</v>
+      </c>
+      <c r="G13" s="7">
+        <v>0.21954689767454627</v>
+      </c>
+      <c r="H13" s="7">
+        <v>-5.5288962671237861E-2</v>
+      </c>
+      <c r="I13" s="7">
+        <v>-0.11495309722722752</v>
+      </c>
+      <c r="J13" s="7">
+        <v>2.2515718230161602E-2</v>
+      </c>
+      <c r="K13" s="7">
+        <v>-0.10166223966007563</v>
+      </c>
+      <c r="L13" s="7">
         <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="B14" s="6">
-        <v>0.44990182198804424</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-3.9908472217596892E-2</v>
-      </c>
-      <c r="D14" s="6">
-        <v>0.5241423501457344</v>
-      </c>
-      <c r="E14" s="6">
-        <v>0.39735670146575258</v>
-      </c>
-      <c r="F14" s="6">
-        <v>0.3274317627387065</v>
-      </c>
-      <c r="G14" s="6">
-        <v>0.23435387543278829</v>
-      </c>
-      <c r="H14" s="6">
-        <v>4.854446556334472E-2</v>
-      </c>
-      <c r="I14" s="6">
-        <v>5.0753074389224696E-2</v>
-      </c>
-      <c r="J14" s="6">
-        <v>0.13756442131258245</v>
-      </c>
-      <c r="K14" s="6">
-        <v>-3.4154166206675093E-2</v>
-      </c>
-      <c r="L14" s="6">
-        <v>3</v>
+      <c r="B14" s="7">
+        <v>0.38881280370071181</v>
+      </c>
+      <c r="C14" s="7">
+        <v>-0.3449275073885707</v>
+      </c>
+      <c r="D14" s="7">
+        <v>0.74040551381956066</v>
+      </c>
+      <c r="E14" s="7">
+        <v>0.26584985448631565</v>
+      </c>
+      <c r="F14" s="7">
+        <v>0.27122796028270102</v>
+      </c>
+      <c r="G14" s="7">
+        <v>0.13640301594688375</v>
+      </c>
+      <c r="H14" s="7">
+        <v>-0.71471875679789743</v>
+      </c>
+      <c r="I14" s="7">
+        <v>-3.8540779118419355E-2</v>
+      </c>
+      <c r="J14" s="7">
+        <v>9.4243876670835032E-4</v>
+      </c>
+      <c r="K14" s="7">
+        <v>-3.7038159294015466E-2</v>
+      </c>
+      <c r="L14" s="7">
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="B15" s="6">
-        <v>0.48195448089155796</v>
-      </c>
-      <c r="C15" s="6">
-        <v>0.11162085504051951</v>
-      </c>
-      <c r="D15" s="6">
-        <v>2.0326810607036561E-2</v>
-      </c>
-      <c r="E15" s="6">
-        <v>0.81793256629235334</v>
-      </c>
-      <c r="F15" s="6">
-        <v>0.70932323159998212</v>
-      </c>
-      <c r="G15" s="6">
-        <v>0.29724487362987351</v>
-      </c>
-      <c r="H15" s="6">
-        <v>-5.2242901122311482E-2</v>
-      </c>
-      <c r="I15" s="6">
-        <v>0.18578366584026185</v>
-      </c>
-      <c r="J15" s="6">
-        <v>0.25598395474631641</v>
-      </c>
-      <c r="K15" s="6">
-        <v>7.6211149597577481E-3</v>
-      </c>
-      <c r="L15" s="6">
-        <v>3</v>
+      <c r="A15" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B15" s="7">
+        <v>0.45057033576190547</v>
+      </c>
+      <c r="C15" s="7">
+        <v>-0.12128517025996415</v>
+      </c>
+      <c r="D15" s="7">
+        <v>0.62138813419833572</v>
+      </c>
+      <c r="E15" s="7">
+        <v>0.29947778206968312</v>
+      </c>
+      <c r="F15" s="7">
+        <v>0.3594629077139137</v>
+      </c>
+      <c r="G15" s="7">
+        <v>0.26539025849349274</v>
+      </c>
+      <c r="H15" s="7">
+        <v>-0.1520312446618681</v>
+      </c>
+      <c r="I15" s="7">
+        <v>-4.4681454477457028E-2</v>
+      </c>
+      <c r="J15" s="7">
+        <v>1.6371245124973035E-2</v>
+      </c>
+      <c r="K15" s="7">
+        <v>-6.3330335111041761E-2</v>
+      </c>
+      <c r="L15" s="7">
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="B16" s="6">
-        <v>0.40077869375600911</v>
-      </c>
-      <c r="C16" s="6">
-        <v>5.5550939680041093E-2</v>
-      </c>
-      <c r="D16" s="6">
-        <v>0.37109435595794277</v>
-      </c>
-      <c r="E16" s="6">
-        <v>0.42640952845453334</v>
-      </c>
-      <c r="F16" s="6">
-        <v>0.39989585047638104</v>
-      </c>
-      <c r="G16" s="6">
-        <v>0.13696645438974911</v>
-      </c>
-      <c r="H16" s="6">
-        <v>-0.19107782963953579</v>
-      </c>
-      <c r="I16" s="6">
-        <v>0.25121131474415143</v>
-      </c>
-      <c r="J16" s="6">
-        <v>0.29717115407059369</v>
-      </c>
-      <c r="K16" s="6">
-        <v>-3.6576876044211705E-2</v>
-      </c>
-      <c r="L16" s="6">
+      <c r="A16" s="6">
+        <v>1</v>
+      </c>
+      <c r="B16" s="7">
+        <v>0.4512388495357666</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-0.20266186830233138</v>
+      </c>
+      <c r="D16" s="7">
+        <v>0.71863391825093703</v>
+      </c>
+      <c r="E16" s="7">
+        <v>0.20159886267361371</v>
+      </c>
+      <c r="F16" s="7">
+        <v>0.39149405268912085</v>
+      </c>
+      <c r="G16" s="7">
+        <v>0.29642664155419723</v>
+      </c>
+      <c r="H16" s="7">
+        <v>-0.35260695488708094</v>
+      </c>
+      <c r="I16" s="7">
+        <v>-0.14011598334413874</v>
+      </c>
+      <c r="J16" s="7">
+        <v>-0.10482193106263639</v>
+      </c>
+      <c r="K16" s="7">
+        <v>-9.2506504015408428E-2</v>
+      </c>
+      <c r="L16" s="7">
         <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="B17" s="6">
-        <v>0.5064459430469832</v>
-      </c>
-      <c r="C17" s="6">
-        <v>0.15438040708179887</v>
-      </c>
-      <c r="D17" s="6">
-        <v>0.33078177034630302</v>
-      </c>
-      <c r="E17" s="6">
-        <v>0.73158238816779464</v>
-      </c>
-      <c r="F17" s="6">
-        <v>0.72143975646172065</v>
-      </c>
-      <c r="G17" s="6">
-        <v>0.2055756348072805</v>
-      </c>
-      <c r="H17" s="6">
-        <v>0.15899980977589198</v>
-      </c>
-      <c r="I17" s="6">
-        <v>0.17734910318448613</v>
-      </c>
-      <c r="J17" s="6">
-        <v>0.14413745539804992</v>
-      </c>
-      <c r="K17" s="6">
-        <v>2.897152729026627E-2</v>
-      </c>
-      <c r="L17" s="6">
+      <c r="A17" s="6">
+        <v>2</v>
+      </c>
+      <c r="B17" s="7">
+        <v>0.44990182198804424</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-3.9908472217596892E-2</v>
+      </c>
+      <c r="D17" s="7">
+        <v>0.5241423501457344</v>
+      </c>
+      <c r="E17" s="7">
+        <v>0.39735670146575258</v>
+      </c>
+      <c r="F17" s="7">
+        <v>0.3274317627387065</v>
+      </c>
+      <c r="G17" s="7">
+        <v>0.23435387543278829</v>
+      </c>
+      <c r="H17" s="7">
+        <v>4.854446556334472E-2</v>
+      </c>
+      <c r="I17" s="7">
+        <v>5.0753074389224696E-2</v>
+      </c>
+      <c r="J17" s="7">
+        <v>0.13756442131258245</v>
+      </c>
+      <c r="K17" s="7">
+        <v>-3.4154166206675093E-2</v>
+      </c>
+      <c r="L17" s="7">
         <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="B18" s="6">
-        <v>0.52217283743410892</v>
-      </c>
-      <c r="C18" s="6">
-        <v>0.1929097495438846</v>
-      </c>
-      <c r="D18" s="6">
-        <v>0.48901782201450961</v>
-      </c>
-      <c r="E18" s="6">
-        <v>0.68941603742594493</v>
-      </c>
-      <c r="F18" s="6">
-        <v>0.74304682596122873</v>
-      </c>
-      <c r="G18" s="6">
-        <v>0.11873702603220478</v>
-      </c>
-      <c r="H18" s="6">
-        <v>1.8595335110253564E-2</v>
-      </c>
-      <c r="I18" s="6">
-        <v>0.34482503456907088</v>
-      </c>
-      <c r="J18" s="6">
-        <v>0.35279853664343247</v>
-      </c>
-      <c r="K18" s="6">
-        <v>1.8520649376419434E-2</v>
-      </c>
-      <c r="L18" s="6">
-        <v>3</v>
+      <c r="A18" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B18" s="7">
+        <v>0.34907312398530305</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-0.40837683694314686</v>
+      </c>
+      <c r="D18" s="7">
+        <v>0.79363465459184379</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0.22711897393053135</v>
+      </c>
+      <c r="F18" s="7">
+        <v>0.21688852191671937</v>
+      </c>
+      <c r="G18" s="7">
+        <v>8.3745008193117809E-2</v>
+      </c>
+      <c r="H18" s="7">
+        <v>-0.7605302378279224</v>
+      </c>
+      <c r="I18" s="7">
+        <v>-4.2253288521562925E-2</v>
+      </c>
+      <c r="J18" s="7">
+        <v>-1.5078302276993935E-2</v>
+      </c>
+      <c r="K18" s="7">
+        <v>-5.0634569573691328E-2</v>
+      </c>
+      <c r="L18" s="7">
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B19" s="6">
-        <v>0.46078989735469544</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-0.10502805488041107</v>
-      </c>
-      <c r="D19" s="6">
-        <v>0.30681409429287076</v>
-      </c>
-      <c r="E19" s="6">
-        <v>0.59108986478998338</v>
-      </c>
-      <c r="F19" s="6">
-        <v>0.56423678188226822</v>
-      </c>
-      <c r="G19" s="6">
-        <v>0.30035713235677841</v>
-      </c>
-      <c r="H19" s="6">
-        <v>-0.15147935298691717</v>
-      </c>
-      <c r="I19" s="6">
-        <v>-1.0003200039276109E-2</v>
-      </c>
-      <c r="J19" s="6">
-        <v>5.0877770034051827E-2</v>
-      </c>
-      <c r="K19" s="6">
-        <v>-0.13415121381316919</v>
-      </c>
-      <c r="L19" s="6">
-        <v>36</v>
+      <c r="A19" s="6">
+        <v>1</v>
+      </c>
+      <c r="B19" s="7">
+        <v>0.23945204122230654</v>
+      </c>
+      <c r="C19" s="7">
+        <v>-0.52282563620483136</v>
+      </c>
+      <c r="D19" s="7">
+        <v>0.89527034779397141</v>
+      </c>
+      <c r="E19" s="7">
+        <v>1.0978003348556734E-2</v>
+      </c>
+      <c r="F19" s="7">
+        <v>8.6394773544027723E-3</v>
+      </c>
+      <c r="G19" s="7">
+        <v>1.7659162541958501E-2</v>
+      </c>
+      <c r="H19" s="7">
+        <v>-1.1238611336052751</v>
+      </c>
+      <c r="I19" s="7">
+        <v>-3.7063404660596287E-2</v>
+      </c>
+      <c r="J19" s="7">
+        <v>-2.7233731846902993E-2</v>
+      </c>
+      <c r="K19" s="7">
+        <v>-2.8323988096141745E-2</v>
+      </c>
+      <c r="L19" s="7">
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="5">
-        <v>1</v>
-      </c>
-      <c r="B20" s="6">
-        <v>0.49136617039776315</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-6.5490092569971167E-2</v>
-      </c>
-      <c r="D20" s="6">
-        <v>0.28555692144779155</v>
-      </c>
-      <c r="E20" s="6">
-        <v>0.62890345314592633</v>
-      </c>
-      <c r="F20" s="6">
-        <v>0.59677109026785535</v>
-      </c>
-      <c r="G20" s="6">
-        <v>0.39618498396193502</v>
-      </c>
-      <c r="H20" s="6">
-        <v>-0.24823665975630321</v>
-      </c>
-      <c r="I20" s="6">
-        <v>0.10992776463288893</v>
-      </c>
-      <c r="J20" s="6">
-        <v>0.15704589057051363</v>
-      </c>
-      <c r="K20" s="6">
-        <v>-9.8160140709700763E-2</v>
-      </c>
-      <c r="L20" s="6">
-        <v>18</v>
+      <c r="A20" s="6">
+        <v>2</v>
+      </c>
+      <c r="B20" s="7">
+        <v>0.45869420674829953</v>
+      </c>
+      <c r="C20" s="7">
+        <v>-0.29392803768146242</v>
+      </c>
+      <c r="D20" s="7">
+        <v>0.69199896138971606</v>
+      </c>
+      <c r="E20" s="7">
+        <v>0.44325994451250589</v>
+      </c>
+      <c r="F20" s="7">
+        <v>0.425137566479036</v>
+      </c>
+      <c r="G20" s="7">
+        <v>0.14983085384427711</v>
+      </c>
+      <c r="H20" s="7">
+        <v>-0.39719934205056995</v>
+      </c>
+      <c r="I20" s="7">
+        <v>-4.7443172382529548E-2</v>
+      </c>
+      <c r="J20" s="7">
+        <v>-2.922872707084872E-3</v>
+      </c>
+      <c r="K20" s="7">
+        <v>-7.29451510512409E-2</v>
+      </c>
+      <c r="L20" s="7">
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="B21" s="6">
-        <v>0.51317131096266033</v>
-      </c>
-      <c r="C21" s="6">
-        <v>0.32132886892025753</v>
-      </c>
-      <c r="D21" s="6">
-        <v>0.33994010061038415</v>
-      </c>
-      <c r="E21" s="6">
-        <v>0.72784003508917927</v>
-      </c>
-      <c r="F21" s="6">
-        <v>0.60923846574490925</v>
-      </c>
-      <c r="G21" s="6">
-        <v>0.41791020802472856</v>
-      </c>
-      <c r="H21" s="6">
-        <v>0.1051133452605461</v>
-      </c>
-      <c r="I21" s="6">
-        <v>0.6225606650600789</v>
-      </c>
-      <c r="J21" s="6">
-        <v>0.56202121591119469</v>
-      </c>
-      <c r="K21" s="6">
-        <v>3.4839889959073674E-2</v>
-      </c>
-      <c r="L21" s="6">
-        <v>3</v>
+      <c r="A21" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B21" s="7">
+        <v>0.36679495135492696</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-0.50512051496260102</v>
+      </c>
+      <c r="D21" s="7">
+        <v>0.80619375266850302</v>
+      </c>
+      <c r="E21" s="7">
+        <v>0.27095280745873268</v>
+      </c>
+      <c r="F21" s="7">
+        <v>0.23733245121746985</v>
+      </c>
+      <c r="G21" s="7">
+        <v>6.0073781154040662E-2</v>
+      </c>
+      <c r="H21" s="7">
+        <v>-1.2315947879039022</v>
+      </c>
+      <c r="I21" s="7">
+        <v>-2.8687594356238102E-2</v>
+      </c>
+      <c r="J21" s="7">
+        <v>1.5343734521459558E-3</v>
+      </c>
+      <c r="K21" s="7">
+        <v>2.8504268026866945E-3</v>
+      </c>
+      <c r="L21" s="7">
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="B22" s="6">
-        <v>0.23945204122230654</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-0.52282563620483136</v>
-      </c>
-      <c r="D22" s="6">
-        <v>0.89527034779397141</v>
-      </c>
-      <c r="E22" s="6">
-        <v>1.0978003348556734E-2</v>
-      </c>
-      <c r="F22" s="6">
-        <v>8.6394773544027723E-3</v>
-      </c>
-      <c r="G22" s="6">
-        <v>1.7659162541958501E-2</v>
-      </c>
-      <c r="H22" s="6">
-        <v>-1.1238611336052751</v>
-      </c>
-      <c r="I22" s="6">
-        <v>-3.7063404660596287E-2</v>
-      </c>
-      <c r="J22" s="6">
-        <v>-2.7233731846902993E-2</v>
-      </c>
-      <c r="K22" s="6">
-        <v>-2.8323988096141745E-2</v>
-      </c>
-      <c r="L22" s="6">
+      <c r="A22" s="6">
+        <v>1</v>
+      </c>
+      <c r="B22" s="7">
+        <v>0.22533733461207861</v>
+      </c>
+      <c r="C22" s="7">
+        <v>-0.48731451134657489</v>
+      </c>
+      <c r="D22" s="7">
+        <v>0.8894645808774998</v>
+      </c>
+      <c r="E22" s="7">
+        <v>2.0900651997009193E-2</v>
+      </c>
+      <c r="F22" s="7">
+        <v>1.1338287286547141E-2</v>
+      </c>
+      <c r="G22" s="7">
+        <v>-1.734343660586557E-4</v>
+      </c>
+      <c r="H22" s="7">
+        <v>-1.0664658686725679</v>
+      </c>
+      <c r="I22" s="7">
+        <v>6.2792827270556168E-3</v>
+      </c>
+      <c r="J22" s="7">
+        <v>1.0143400614503991E-2</v>
+      </c>
+      <c r="K22" s="7">
+        <v>-4.8260770089125033E-3</v>
+      </c>
+      <c r="L22" s="7">
         <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="B23" s="6">
-        <v>0.67460144977308334</v>
-      </c>
-      <c r="C23" s="6">
-        <v>0.38534329454496929</v>
-      </c>
-      <c r="D23" s="6">
-        <v>4.2739871423871624E-2</v>
-      </c>
-      <c r="E23" s="6">
-        <v>0.95125742303489014</v>
-      </c>
-      <c r="F23" s="6">
-        <v>0.88858528057444663</v>
-      </c>
-      <c r="G23" s="6">
-        <v>0.81635008842753065</v>
-      </c>
-      <c r="H23" s="6">
-        <v>4.7462966188487277E-2</v>
-      </c>
-      <c r="I23" s="6">
-        <v>0.72191412645764663</v>
-      </c>
-      <c r="J23" s="6">
-        <v>0.56718001929156558</v>
-      </c>
-      <c r="K23" s="6">
-        <v>0.18383805512103699</v>
-      </c>
-      <c r="L23" s="6">
+      <c r="A23" s="6">
+        <v>2</v>
+      </c>
+      <c r="B23" s="7">
+        <v>0.5082525680977753</v>
+      </c>
+      <c r="C23" s="7">
+        <v>-0.52292651857862715</v>
+      </c>
+      <c r="D23" s="7">
+        <v>0.72292292445950623</v>
+      </c>
+      <c r="E23" s="7">
+        <v>0.52100496292045617</v>
+      </c>
+      <c r="F23" s="7">
+        <v>0.46332661514839257</v>
+      </c>
+      <c r="G23" s="7">
+        <v>0.12032099667413998</v>
+      </c>
+      <c r="H23" s="7">
+        <v>-1.3967237071352363</v>
+      </c>
+      <c r="I23" s="7">
+        <v>-6.3654471439531818E-2</v>
+      </c>
+      <c r="J23" s="7">
+        <v>-7.0746537102120794E-3</v>
+      </c>
+      <c r="K23" s="7">
+        <v>1.0526930614285892E-2</v>
+      </c>
+      <c r="L23" s="7">
         <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="B24" s="6">
-        <v>0.52677606280705358</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-0.95031401655384207</v>
-      </c>
-      <c r="D24" s="6">
-        <v>3.847145434940747E-2</v>
-      </c>
-      <c r="E24" s="6">
-        <v>0.63550605981186614</v>
-      </c>
-      <c r="F24" s="6">
-        <v>0.59431064495391916</v>
-      </c>
-      <c r="G24" s="6">
-        <v>0.54448367983785184</v>
-      </c>
-      <c r="H24" s="6">
-        <v>-0.33329861152193624</v>
-      </c>
-      <c r="I24" s="6">
-        <v>-1.3344651140404948</v>
-      </c>
-      <c r="J24" s="6">
-        <v>-1.0647241388582036</v>
-      </c>
-      <c r="K24" s="6">
-        <v>-0.74479003717412351</v>
-      </c>
-      <c r="L24" s="6">
-        <v>3</v>
+      <c r="A24" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B24" s="7">
+        <v>0.57726562239393553</v>
+      </c>
+      <c r="C24" s="7">
+        <v>4.9317320570717998E-3</v>
+      </c>
+      <c r="D24" s="7">
+        <v>5.5596361783147703E-2</v>
+      </c>
+      <c r="E24" s="7">
+        <v>0.86584060126161033</v>
+      </c>
+      <c r="F24" s="7">
+        <v>0.80301912935814257</v>
+      </c>
+      <c r="G24" s="7">
+        <v>0.5504144005818552</v>
+      </c>
+      <c r="H24" s="7">
+        <v>-7.0480482010203066E-3</v>
+      </c>
+      <c r="I24" s="7">
+        <v>9.2256824250051592E-2</v>
+      </c>
+      <c r="J24" s="7">
+        <v>0.11354400631668025</v>
+      </c>
+      <c r="K24" s="7">
+        <v>-0.15217485555876856</v>
+      </c>
+      <c r="L24" s="7">
+        <v>18</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="B25" s="6">
-        <v>0.55260196350000446</v>
-      </c>
-      <c r="C25" s="6">
-        <v>8.6096849761306923E-2</v>
-      </c>
-      <c r="D25" s="6">
-        <v>9.2256390976537261E-2</v>
-      </c>
-      <c r="E25" s="6">
-        <v>0.81968169121487156</v>
-      </c>
-      <c r="F25" s="6">
-        <v>0.74776498923801249</v>
-      </c>
-      <c r="G25" s="6">
-        <v>0.47306152227834614</v>
-      </c>
-      <c r="H25" s="6">
-        <v>4.1738881638607672E-2</v>
-      </c>
-      <c r="I25" s="6">
-        <v>1.4359642655774635E-2</v>
-      </c>
-      <c r="J25" s="6">
-        <v>0.12750077329609397</v>
-      </c>
-      <c r="K25" s="6">
-        <v>-3.3430254747818938E-2</v>
-      </c>
-      <c r="L25" s="6">
-        <v>3</v>
+      <c r="A25" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B25" s="7">
+        <v>0.57289566398559288</v>
+      </c>
+      <c r="C25" s="7">
+        <v>0.24498100126893177</v>
+      </c>
+      <c r="D25" s="7">
+        <v>2.1464379226993045E-2</v>
+      </c>
+      <c r="E25" s="7">
+        <v>0.88148639171521248</v>
+      </c>
+      <c r="F25" s="7">
+        <v>0.79326574533754435</v>
+      </c>
+      <c r="G25" s="7">
+        <v>0.5606376690495779</v>
+      </c>
+      <c r="H25" s="7">
+        <v>-3.1824165996228226E-2</v>
+      </c>
+      <c r="I25" s="7">
+        <v>0.4447628731768572</v>
+      </c>
+      <c r="J25" s="7">
+        <v>0.34347618314686074</v>
+      </c>
+      <c r="K25" s="7">
+        <v>0.18120787767419835</v>
+      </c>
+      <c r="L25" s="7">
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A26" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="B26" s="6">
-        <v>0.44159419412147088</v>
-      </c>
-      <c r="C26" s="6">
-        <v>0.28743008411231286</v>
-      </c>
-      <c r="D26" s="6">
-        <v>0.30466336353257728</v>
-      </c>
-      <c r="E26" s="6">
-        <v>0.62815750637619383</v>
-      </c>
-      <c r="F26" s="6">
-        <v>0.73208768374144262</v>
-      </c>
-      <c r="G26" s="6">
-        <v>0.10764524266119437</v>
-      </c>
-      <c r="H26" s="6">
-        <v>-0.2265754064982485</v>
-      </c>
-      <c r="I26" s="6">
-        <v>0.67226067232492459</v>
-      </c>
-      <c r="J26" s="6">
-        <v>0.77753120562933453</v>
-      </c>
-      <c r="K26" s="6">
-        <v>-1.0945093202310654E-3</v>
-      </c>
-      <c r="L26" s="6">
+      <c r="A26" s="6">
+        <v>1</v>
+      </c>
+      <c r="B26" s="7">
+        <v>0.66383684707962776</v>
+      </c>
+      <c r="C26" s="7">
+        <v>0.37834114749734399</v>
+      </c>
+      <c r="D26" s="7">
+        <v>2.2601947846949532E-2</v>
+      </c>
+      <c r="E26" s="7">
+        <v>0.94504021713807151</v>
+      </c>
+      <c r="F26" s="7">
+        <v>0.87720825907510669</v>
+      </c>
+      <c r="G26" s="7">
+        <v>0.82403046446928219</v>
+      </c>
+      <c r="H26" s="7">
+        <v>-1.1405430870144969E-2</v>
+      </c>
+      <c r="I26" s="7">
+        <v>0.70374208051345255</v>
+      </c>
+      <c r="J26" s="7">
+        <v>0.43096841154740506</v>
+      </c>
+      <c r="K26" s="7">
+        <v>0.354794640388639</v>
+      </c>
+      <c r="L26" s="7">
         <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A27" s="5">
+      <c r="A27" s="6">
         <v>2</v>
       </c>
-      <c r="B27" s="6">
-        <v>0.43021362431162768</v>
-      </c>
-      <c r="C27" s="6">
-        <v>-0.14456601719085102</v>
-      </c>
-      <c r="D27" s="6">
-        <v>0.32807126713794998</v>
-      </c>
-      <c r="E27" s="6">
-        <v>0.55327627643403998</v>
-      </c>
-      <c r="F27" s="6">
-        <v>0.53170247349668132</v>
-      </c>
-      <c r="G27" s="6">
-        <v>0.20452928075162183</v>
-      </c>
-      <c r="H27" s="6">
-        <v>-5.4722046217531108E-2</v>
-      </c>
-      <c r="I27" s="6">
-        <v>-0.12993416471144117</v>
-      </c>
-      <c r="J27" s="6">
-        <v>-5.5290350502409921E-2</v>
-      </c>
-      <c r="K27" s="6">
-        <v>-0.17014228691663763</v>
-      </c>
-      <c r="L27" s="6">
-        <v>18</v>
+      <c r="B27" s="7">
+        <v>0.48195448089155796</v>
+      </c>
+      <c r="C27" s="7">
+        <v>0.11162085504051951</v>
+      </c>
+      <c r="D27" s="7">
+        <v>2.0326810607036561E-2</v>
+      </c>
+      <c r="E27" s="7">
+        <v>0.81793256629235334</v>
+      </c>
+      <c r="F27" s="7">
+        <v>0.70932323159998212</v>
+      </c>
+      <c r="G27" s="7">
+        <v>0.29724487362987351</v>
+      </c>
+      <c r="H27" s="7">
+        <v>-5.2242901122311482E-2</v>
+      </c>
+      <c r="I27" s="7">
+        <v>0.18578366584026185</v>
+      </c>
+      <c r="J27" s="7">
+        <v>0.25598395474631641</v>
+      </c>
+      <c r="K27" s="7">
+        <v>7.6211149597577481E-3</v>
+      </c>
+      <c r="L27" s="7">
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A28" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="B28" s="6">
-        <v>0.35825685169351607</v>
-      </c>
-      <c r="C28" s="6">
-        <v>-3.0880929320347097E-2</v>
-      </c>
-      <c r="D28" s="6">
-        <v>0.28533446242107346</v>
-      </c>
-      <c r="E28" s="6">
-        <v>0.43946026499254165</v>
-      </c>
-      <c r="F28" s="6">
-        <v>0.42850889770246364</v>
-      </c>
-      <c r="G28" s="6">
-        <v>0.12134878091813073</v>
-      </c>
-      <c r="H28" s="6">
-        <v>3.859983247835852E-2</v>
-      </c>
-      <c r="I28" s="6">
-        <v>-7.1986561983173811E-2</v>
-      </c>
-      <c r="J28" s="6">
-        <v>5.7225138074246951E-3</v>
-      </c>
-      <c r="K28" s="6">
-        <v>-4.4247809198682285E-2</v>
-      </c>
-      <c r="L28" s="6">
-        <v>3</v>
+      <c r="A28" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B28" s="7">
+        <v>0.5916742438503807</v>
+      </c>
+      <c r="C28" s="7">
+        <v>2.1618186547838526E-2</v>
+      </c>
+      <c r="D28" s="7">
+        <v>7.4316101542125798E-2</v>
+      </c>
+      <c r="E28" s="7">
+        <v>0.84145461438764968</v>
+      </c>
+      <c r="F28" s="7">
+        <v>0.79243311780605863</v>
+      </c>
+      <c r="G28" s="7">
+        <v>0.64234773385073574</v>
+      </c>
+      <c r="H28" s="7">
+        <v>2.0123596619915588E-3</v>
+      </c>
+      <c r="I28" s="7">
+        <v>0.21007019900077537</v>
+      </c>
+      <c r="J28" s="7">
+        <v>0.27020125508512705</v>
+      </c>
+      <c r="K28" s="7">
+        <v>-0.28717971059493147</v>
+      </c>
+      <c r="L28" s="7">
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A29" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="B29" s="6">
-        <v>0.45869420674829953</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-0.29392803768146242</v>
-      </c>
-      <c r="D29" s="6">
-        <v>0.69199896138971606</v>
-      </c>
-      <c r="E29" s="6">
-        <v>0.44325994451250589</v>
-      </c>
-      <c r="F29" s="6">
-        <v>0.425137566479036</v>
-      </c>
-      <c r="G29" s="6">
-        <v>0.14983085384427711</v>
-      </c>
-      <c r="H29" s="6">
-        <v>-0.39719934205056995</v>
-      </c>
-      <c r="I29" s="6">
-        <v>-4.7443172382529548E-2</v>
-      </c>
-      <c r="J29" s="6">
-        <v>-2.922872707084872E-3</v>
-      </c>
-      <c r="K29" s="6">
-        <v>-7.29451510512409E-2</v>
-      </c>
-      <c r="L29" s="6">
+      <c r="A29" s="6">
+        <v>1</v>
+      </c>
+      <c r="B29" s="7">
+        <v>0.67460144977308334</v>
+      </c>
+      <c r="C29" s="7">
+        <v>0.38534329454496929</v>
+      </c>
+      <c r="D29" s="7">
+        <v>4.2739871423871624E-2</v>
+      </c>
+      <c r="E29" s="7">
+        <v>0.95125742303489014</v>
+      </c>
+      <c r="F29" s="7">
+        <v>0.88858528057444663</v>
+      </c>
+      <c r="G29" s="7">
+        <v>0.81635008842753065</v>
+      </c>
+      <c r="H29" s="7">
+        <v>4.7462966188487277E-2</v>
+      </c>
+      <c r="I29" s="7">
+        <v>0.72191412645764663</v>
+      </c>
+      <c r="J29" s="7">
+        <v>0.56718001929156558</v>
+      </c>
+      <c r="K29" s="7">
+        <v>0.18383805512103699</v>
+      </c>
+      <c r="L29" s="7">
         <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="B30" s="6">
+      <c r="A30" s="6">
+        <v>2</v>
+      </c>
+      <c r="B30" s="7">
         <v>0.50874703792767817</v>
       </c>
-      <c r="C30" s="6">
+      <c r="C30" s="7">
         <v>-0.34210692144929222</v>
       </c>
-      <c r="D30" s="6">
+      <c r="D30" s="7">
         <v>0.10589233166037998</v>
       </c>
-      <c r="E30" s="6">
+      <c r="E30" s="7">
         <v>0.73165180574040922</v>
       </c>
-      <c r="F30" s="6">
+      <c r="F30" s="7">
         <v>0.69628095503767062</v>
       </c>
-      <c r="G30" s="6">
+      <c r="G30" s="7">
         <v>0.46834537927394077</v>
       </c>
-      <c r="H30" s="6">
+      <c r="H30" s="7">
         <v>-4.3438246864504156E-2</v>
       </c>
-      <c r="I30" s="6">
+      <c r="I30" s="7">
         <v>-0.30177372845609596</v>
       </c>
-      <c r="J30" s="6">
+      <c r="J30" s="7">
         <v>-2.6777509121311483E-2</v>
       </c>
-      <c r="K30" s="6">
+      <c r="K30" s="7">
         <v>-0.75819747631089973</v>
       </c>
-      <c r="L30" s="6">
+      <c r="L30" s="7">
         <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A31" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="B31" s="6">
-        <v>0.39702301547442248</v>
-      </c>
-      <c r="C31" s="6">
-        <v>5.8966906702589599E-3</v>
-      </c>
-      <c r="D31" s="6">
-        <v>0.34656973195086449</v>
-      </c>
-      <c r="E31" s="6">
-        <v>0.39786669244968992</v>
-      </c>
-      <c r="F31" s="6">
-        <v>0.40710812506509558</v>
-      </c>
-      <c r="G31" s="6">
-        <v>0.13228793371089684</v>
-      </c>
-      <c r="H31" s="6">
-        <v>-0.10848034059942126</v>
-      </c>
-      <c r="I31" s="6">
-        <v>4.566044286221304E-2</v>
-      </c>
-      <c r="J31" s="6">
-        <v>9.1701406248638803E-2</v>
-      </c>
-      <c r="K31" s="6">
-        <v>-1.7638848428519632E-2</v>
-      </c>
-      <c r="L31" s="6">
-        <v>3</v>
+      <c r="A31" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B31" s="7">
+        <v>0.56722695934583278</v>
+      </c>
+      <c r="C31" s="7">
+        <v>-0.251803991645555</v>
+      </c>
+      <c r="D31" s="7">
+        <v>7.1008604580324222E-2</v>
+      </c>
+      <c r="E31" s="7">
+        <v>0.87458079768196939</v>
+      </c>
+      <c r="F31" s="7">
+        <v>0.82335852493082451</v>
+      </c>
+      <c r="G31" s="7">
+        <v>0.4482577988452518</v>
+      </c>
+      <c r="H31" s="7">
+        <v>8.6676617311757433E-3</v>
+      </c>
+      <c r="I31" s="7">
+        <v>-0.37806259942747783</v>
+      </c>
+      <c r="J31" s="7">
+        <v>-0.27304541928194698</v>
+      </c>
+      <c r="K31" s="7">
+        <v>-0.35055273375557272</v>
+      </c>
+      <c r="L31" s="7">
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A32" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="B32" s="6">
-        <v>0.4786123754013995</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-0.123982964255128</v>
-      </c>
-      <c r="D32" s="6">
-        <v>0.16785333055690307</v>
-      </c>
-      <c r="E32" s="6">
-        <v>0.79418461507534188</v>
-      </c>
-      <c r="F32" s="6">
-        <v>0.66900922325157242</v>
-      </c>
-      <c r="G32" s="6">
-        <v>0.25189736152505154</v>
-      </c>
-      <c r="H32" s="6">
-        <v>0.14849347486103057</v>
-      </c>
-      <c r="I32" s="6">
-        <v>-0.23117965765873297</v>
-      </c>
-      <c r="J32" s="6">
-        <v>-0.31002408837517348</v>
-      </c>
-      <c r="K32" s="6">
-        <v>-4.6403778305833678E-2</v>
-      </c>
-      <c r="L32" s="6">
+      <c r="A32" s="6">
+        <v>1</v>
+      </c>
+      <c r="B32" s="7">
+        <v>0.60229065167004137</v>
+      </c>
+      <c r="C32" s="7">
+        <v>-0.33600027190517251</v>
+      </c>
+      <c r="D32" s="7">
+        <v>5.3776672514237039E-2</v>
+      </c>
+      <c r="E32" s="7">
+        <v>0.93813990009815795</v>
+      </c>
+      <c r="F32" s="7">
+        <v>0.88463092703335322</v>
+      </c>
+      <c r="G32" s="7">
+        <v>0.53892571752715956</v>
+      </c>
+      <c r="H32" s="7">
+        <v>-8.3634740883355332E-2</v>
+      </c>
+      <c r="I32" s="7">
+        <v>-0.55814243588267753</v>
+      </c>
+      <c r="J32" s="7">
+        <v>-0.33188723970526923</v>
+      </c>
+      <c r="K32" s="7">
+        <v>-0.34567011051925561</v>
+      </c>
+      <c r="L32" s="7">
         <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A33" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="B33" s="6">
-        <v>0.37994825862445031</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-8.2393941109135269E-2</v>
-      </c>
-      <c r="D33" s="6">
-        <v>0.37077878484876309</v>
-      </c>
-      <c r="E33" s="6">
-        <v>0.513234335833752</v>
-      </c>
-      <c r="F33" s="6">
-        <v>0.56417007344424963</v>
-      </c>
-      <c r="G33" s="6">
-        <v>0.10346537523743403</v>
-      </c>
-      <c r="H33" s="6">
-        <v>3.3692344869919677E-2</v>
-      </c>
-      <c r="I33" s="6">
-        <v>-0.17288231065032766</v>
-      </c>
-      <c r="J33" s="6">
-        <v>-8.9441552866953211E-2</v>
-      </c>
-      <c r="K33" s="6">
-        <v>-8.1420658204649374E-2</v>
-      </c>
-      <c r="L33" s="6">
+      <c r="A33" s="6">
+        <v>2</v>
+      </c>
+      <c r="B33" s="7">
+        <v>0.53216326702162431</v>
+      </c>
+      <c r="C33" s="7">
+        <v>-0.16760771138593752</v>
+      </c>
+      <c r="D33" s="7">
+        <v>8.8240536646411405E-2</v>
+      </c>
+      <c r="E33" s="7">
+        <v>0.81102169526578083</v>
+      </c>
+      <c r="F33" s="7">
+        <v>0.76208612282829591</v>
+      </c>
+      <c r="G33" s="7">
+        <v>0.35758988016334398</v>
+      </c>
+      <c r="H33" s="7">
+        <v>0.10097006434570682</v>
+      </c>
+      <c r="I33" s="7">
+        <v>-0.19798276297227824</v>
+      </c>
+      <c r="J33" s="7">
+        <v>-0.21420359885862469</v>
+      </c>
+      <c r="K33" s="7">
+        <v>-0.35543535699188977</v>
+      </c>
+      <c r="L33" s="7">
         <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="B34" s="6">
-        <v>0.46821748183280587</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-0.18884650290795241</v>
-      </c>
-      <c r="D34" s="6">
-        <v>0.33861032696283516</v>
-      </c>
-      <c r="E34" s="6">
-        <v>0.58872691388121157</v>
-      </c>
-      <c r="F34" s="6">
-        <v>0.56663887200417062</v>
-      </c>
-      <c r="G34" s="6">
-        <v>0.26795347538557635</v>
-      </c>
-      <c r="H34" s="6">
-        <v>-0.25103609058039261</v>
-      </c>
-      <c r="I34" s="6">
-        <v>-0.11204738702867727</v>
-      </c>
-      <c r="J34" s="6">
-        <v>9.1730363518767837E-3</v>
-      </c>
-      <c r="K34" s="6">
-        <v>-0.13168941275284884</v>
-      </c>
-      <c r="L34" s="6">
-        <v>36</v>
+        <v>102</v>
+      </c>
+      <c r="B34" s="7">
+        <v>0.49874859397857285</v>
+      </c>
+      <c r="C34" s="7">
+        <v>-0.42571389458398518</v>
+      </c>
+      <c r="D34" s="7">
+        <v>0.28580144225817133</v>
+      </c>
+      <c r="E34" s="7">
+        <v>0.54088912989218363</v>
+      </c>
+      <c r="F34" s="7">
+        <v>0.5123178553408041</v>
+      </c>
+      <c r="G34" s="7">
+        <v>0.30222444766807366</v>
+      </c>
+      <c r="H34" s="7">
+        <v>-0.25018601112328909</v>
+      </c>
+      <c r="I34" s="7">
+        <v>-0.43165619876003192</v>
+      </c>
+      <c r="J34" s="7">
+        <v>-0.29374457558387823</v>
+      </c>
+      <c r="K34" s="7">
+        <v>-0.34258676295032586</v>
+      </c>
+      <c r="L34" s="7">
+        <v>18</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A35" s="5">
-        <v>1</v>
-      </c>
-      <c r="B35" s="6">
-        <v>0.4790691005271126</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-0.21242209792696659</v>
-      </c>
-      <c r="D35" s="6">
-        <v>0.34676887547691448</v>
-      </c>
-      <c r="E35" s="6">
-        <v>0.60401944150856524</v>
-      </c>
-      <c r="F35" s="6">
-        <v>0.5940146614746975</v>
-      </c>
-      <c r="G35" s="6">
-        <v>0.31136730640259946</v>
-      </c>
-      <c r="H35" s="6">
-        <v>-0.26855814123394095</v>
-      </c>
-      <c r="I35" s="6">
-        <v>-0.129684107445765</v>
-      </c>
-      <c r="J35" s="6">
-        <v>6.8159302915974621E-2</v>
-      </c>
-      <c r="K35" s="6">
-        <v>-0.15957005718801462</v>
-      </c>
-      <c r="L35" s="6">
-        <v>18</v>
+      <c r="A35" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B35" s="7">
+        <v>0.5131596583517356</v>
+      </c>
+      <c r="C35" s="7">
+        <v>-0.36946013894520019</v>
+      </c>
+      <c r="D35" s="7">
+        <v>0.34637970109837179</v>
+      </c>
+      <c r="E35" s="7">
+        <v>0.49697569679813536</v>
+      </c>
+      <c r="F35" s="7">
+        <v>0.48004011106349626</v>
+      </c>
+      <c r="G35" s="7">
+        <v>0.33983127547673725</v>
+      </c>
+      <c r="H35" s="7">
+        <v>-0.31417620901802262</v>
+      </c>
+      <c r="I35" s="7">
+        <v>-0.34381348123282174</v>
+      </c>
+      <c r="J35" s="7">
+        <v>-0.17595232457623319</v>
+      </c>
+      <c r="K35" s="7">
+        <v>-0.39831534749058012</v>
+      </c>
+      <c r="L35" s="7">
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A36" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="B36" s="6">
-        <v>0.58733400631313504</v>
-      </c>
-      <c r="C36" s="6">
-        <v>0.26916136399111029</v>
-      </c>
-      <c r="D36" s="6">
-        <v>0.45343303929977302</v>
-      </c>
-      <c r="E36" s="6">
-        <v>0.73083718727239122</v>
-      </c>
-      <c r="F36" s="6">
-        <v>0.6601773280567671</v>
-      </c>
-      <c r="G36" s="6">
-        <v>0.48433036883308223</v>
-      </c>
-      <c r="H36" s="6">
-        <v>3.6782046125197303E-2</v>
-      </c>
-      <c r="I36" s="6">
-        <v>0.4642192086577599</v>
-      </c>
-      <c r="J36" s="6">
-        <v>0.553134785453401</v>
-      </c>
-      <c r="K36" s="6">
-        <v>5.5841510110270137E-2</v>
-      </c>
-      <c r="L36" s="6">
+      <c r="A36" s="6">
+        <v>1</v>
+      </c>
+      <c r="B36" s="7">
+        <v>0.62554062294746215</v>
+      </c>
+      <c r="C36" s="7">
+        <v>-0.79447121757044137</v>
+      </c>
+      <c r="D36" s="7">
+        <v>0.32166504623880082</v>
+      </c>
+      <c r="E36" s="7">
+        <v>0.56754186514173732</v>
+      </c>
+      <c r="F36" s="7">
+        <v>0.56018437165061152</v>
+      </c>
+      <c r="G36" s="7">
+        <v>0.54269609656372542</v>
+      </c>
+      <c r="H36" s="7">
+        <v>-0.4372745883965094</v>
+      </c>
+      <c r="I36" s="7">
+        <v>-0.93883827720979485</v>
+      </c>
+      <c r="J36" s="7">
+        <v>-0.64907580322306002</v>
+      </c>
+      <c r="K36" s="7">
+        <v>-0.76005381893694857</v>
+      </c>
+      <c r="L36" s="7">
         <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A37" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="B37" s="6">
-        <v>0.22533733461207861</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-0.48731451134657489</v>
-      </c>
-      <c r="D37" s="6">
-        <v>0.8894645808774998</v>
-      </c>
-      <c r="E37" s="6">
-        <v>2.0900651997009193E-2</v>
-      </c>
-      <c r="F37" s="6">
-        <v>1.1338287286547141E-2</v>
-      </c>
-      <c r="G37" s="6">
-        <v>-1.734343660586557E-4</v>
-      </c>
-      <c r="H37" s="6">
-        <v>-1.0664658686725679</v>
-      </c>
-      <c r="I37" s="6">
-        <v>6.2792827270556168E-3</v>
-      </c>
-      <c r="J37" s="6">
-        <v>1.0143400614503991E-2</v>
-      </c>
-      <c r="K37" s="6">
-        <v>-4.8260770089125033E-3</v>
-      </c>
-      <c r="L37" s="6">
+      <c r="A37" s="6">
+        <v>2</v>
+      </c>
+      <c r="B37" s="7">
+        <v>0.40077869375600911</v>
+      </c>
+      <c r="C37" s="7">
+        <v>5.5550939680041093E-2</v>
+      </c>
+      <c r="D37" s="7">
+        <v>0.37109435595794277</v>
+      </c>
+      <c r="E37" s="7">
+        <v>0.42640952845453334</v>
+      </c>
+      <c r="F37" s="7">
+        <v>0.39989585047638104</v>
+      </c>
+      <c r="G37" s="7">
+        <v>0.13696645438974911</v>
+      </c>
+      <c r="H37" s="7">
+        <v>-0.19107782963953579</v>
+      </c>
+      <c r="I37" s="7">
+        <v>0.25121131474415143</v>
+      </c>
+      <c r="J37" s="7">
+        <v>0.29717115407059369</v>
+      </c>
+      <c r="K37" s="7">
+        <v>-3.6576876044211705E-2</v>
+      </c>
+      <c r="L37" s="7">
         <v>3</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A38" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="B38" s="6">
-        <v>0.60229065167004137</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-0.33600027190517251</v>
-      </c>
-      <c r="D38" s="6">
-        <v>5.3776672514237039E-2</v>
-      </c>
-      <c r="E38" s="6">
-        <v>0.93813990009815795</v>
-      </c>
-      <c r="F38" s="6">
-        <v>0.88463092703335322</v>
-      </c>
-      <c r="G38" s="6">
-        <v>0.53892571752715956</v>
-      </c>
-      <c r="H38" s="6">
-        <v>-8.3634740883355332E-2</v>
-      </c>
-      <c r="I38" s="6">
-        <v>-0.55814243588267753</v>
-      </c>
-      <c r="J38" s="6">
-        <v>-0.33188723970526923</v>
-      </c>
-      <c r="K38" s="6">
-        <v>-0.34567011051925561</v>
-      </c>
-      <c r="L38" s="6">
-        <v>3</v>
+      <c r="A38" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B38" s="7">
+        <v>0.46189953914073795</v>
+      </c>
+      <c r="C38" s="7">
+        <v>-0.47220866294179159</v>
+      </c>
+      <c r="D38" s="7">
+        <v>0.192520593150136</v>
+      </c>
+      <c r="E38" s="7">
+        <v>0.51668637613077806</v>
+      </c>
+      <c r="F38" s="7">
+        <v>0.50070938500950735</v>
+      </c>
+      <c r="G38" s="7">
+        <v>0.33838580677437435</v>
+      </c>
+      <c r="H38" s="7">
+        <v>-0.22088947606067874</v>
+      </c>
+      <c r="I38" s="7">
+        <v>-0.64440233558914084</v>
+      </c>
+      <c r="J38" s="7">
+        <v>-0.48651136630478242</v>
+      </c>
+      <c r="K38" s="7">
+        <v>-0.38121444280132161</v>
+      </c>
+      <c r="L38" s="7">
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A39" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="B39" s="6">
-        <v>0.61728376671648244</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-0.76902066788280932</v>
-      </c>
-      <c r="D39" s="6">
-        <v>0.30629533473189952</v>
-      </c>
-      <c r="E39" s="6">
-        <v>0.75938344980842765</v>
-      </c>
-      <c r="F39" s="6">
-        <v>0.71391276211547494</v>
-      </c>
-      <c r="G39" s="6">
-        <v>0.33577463172092098</v>
-      </c>
-      <c r="H39" s="6">
-        <v>-0.22817724450063639</v>
-      </c>
-      <c r="I39" s="6">
-        <v>-0.62892559498955347</v>
-      </c>
-      <c r="J39" s="6">
-        <v>-0.45477578344153907</v>
-      </c>
-      <c r="K39" s="6">
-        <v>-0.52412395088768349</v>
-      </c>
-      <c r="L39" s="6">
+      <c r="A39" s="6">
+        <v>1</v>
+      </c>
+      <c r="B39" s="7">
+        <v>0.52677606280705358</v>
+      </c>
+      <c r="C39" s="7">
+        <v>-0.95031401655384207</v>
+      </c>
+      <c r="D39" s="7">
+        <v>3.847145434940747E-2</v>
+      </c>
+      <c r="E39" s="7">
+        <v>0.63550605981186614</v>
+      </c>
+      <c r="F39" s="7">
+        <v>0.59431064495391916</v>
+      </c>
+      <c r="G39" s="7">
+        <v>0.54448367983785184</v>
+      </c>
+      <c r="H39" s="7">
+        <v>-0.33329861152193624</v>
+      </c>
+      <c r="I39" s="7">
+        <v>-1.3344651140404948</v>
+      </c>
+      <c r="J39" s="7">
+        <v>-1.0647241388582036</v>
+      </c>
+      <c r="K39" s="7">
+        <v>-0.74479003717412351</v>
+      </c>
+      <c r="L39" s="7">
         <v>3</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A40" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="B40" s="6">
-        <v>0.47495908583426649</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-0.16080439668085547</v>
-      </c>
-      <c r="D40" s="6">
-        <v>1.9852436669001865E-2</v>
-      </c>
-      <c r="E40" s="6">
-        <v>0.7528647174349179</v>
-      </c>
-      <c r="F40" s="6">
-        <v>0.70406124775120971</v>
-      </c>
-      <c r="G40" s="6">
-        <v>0.40073426115798055</v>
-      </c>
-      <c r="H40" s="6">
-        <v>4.2528533301350951E-2</v>
-      </c>
-      <c r="I40" s="6">
-        <v>-0.44158629201752914</v>
-      </c>
-      <c r="J40" s="6">
-        <v>-4.8471008099195689E-3</v>
-      </c>
-      <c r="K40" s="6">
-        <v>-0.22824448664786257</v>
-      </c>
-      <c r="L40" s="6">
+      <c r="A40" s="6">
+        <v>2</v>
+      </c>
+      <c r="B40" s="7">
+        <v>0.39702301547442248</v>
+      </c>
+      <c r="C40" s="7">
+        <v>5.8966906702589599E-3</v>
+      </c>
+      <c r="D40" s="7">
+        <v>0.34656973195086449</v>
+      </c>
+      <c r="E40" s="7">
+        <v>0.39786669244968992</v>
+      </c>
+      <c r="F40" s="7">
+        <v>0.40710812506509558</v>
+      </c>
+      <c r="G40" s="7">
+        <v>0.13228793371089684</v>
+      </c>
+      <c r="H40" s="7">
+        <v>-0.10848034059942126</v>
+      </c>
+      <c r="I40" s="7">
+        <v>4.566044286221304E-2</v>
+      </c>
+      <c r="J40" s="7">
+        <v>9.1701406248638803E-2</v>
+      </c>
+      <c r="K40" s="7">
+        <v>-1.7638848428519632E-2</v>
+      </c>
+      <c r="L40" s="7">
         <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A41" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="B41" s="6">
-        <v>0.36720975801667244</v>
-      </c>
-      <c r="C41" s="6">
-        <v>0.20944589626250218</v>
-      </c>
-      <c r="D41" s="6">
-        <v>0.35779118876907551</v>
-      </c>
-      <c r="E41" s="6">
-        <v>0.42199074244048734</v>
-      </c>
-      <c r="F41" s="6">
-        <v>0.58996741660483298</v>
-      </c>
-      <c r="G41" s="6">
-        <v>0.10861229354251208</v>
-      </c>
-      <c r="H41" s="6">
-        <v>-0.31238157277363476</v>
-      </c>
-      <c r="I41" s="6">
-        <v>0.38005118683035466</v>
-      </c>
-      <c r="J41" s="6">
-        <v>0.63718775538467065</v>
-      </c>
-      <c r="K41" s="6">
-        <v>8.9602771825356434E-2</v>
-      </c>
-      <c r="L41" s="6">
-        <v>3</v>
+      <c r="A41" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B41" s="7">
+        <v>0.52118658444324506</v>
+      </c>
+      <c r="C41" s="7">
+        <v>-0.43547288186496397</v>
+      </c>
+      <c r="D41" s="7">
+        <v>0.31850403252600601</v>
+      </c>
+      <c r="E41" s="7">
+        <v>0.60900531674763736</v>
+      </c>
+      <c r="F41" s="7">
+        <v>0.55620406994940852</v>
+      </c>
+      <c r="G41" s="7">
+        <v>0.22845626075310924</v>
+      </c>
+      <c r="H41" s="7">
+        <v>-0.21549234829116568</v>
+      </c>
+      <c r="I41" s="7">
+        <v>-0.30675277945813312</v>
+      </c>
+      <c r="J41" s="7">
+        <v>-0.21877003587061913</v>
+      </c>
+      <c r="K41" s="7">
+        <v>-0.24823049855907595</v>
+      </c>
+      <c r="L41" s="7">
+        <v>6</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A42" s="5">
-        <v>2</v>
-      </c>
-      <c r="B42" s="6">
-        <v>0.4573658631384992</v>
-      </c>
-      <c r="C42" s="6">
-        <v>-0.1652709078889382</v>
-      </c>
-      <c r="D42" s="6">
-        <v>0.33045177844875584</v>
-      </c>
-      <c r="E42" s="6">
-        <v>0.57343438625385801</v>
-      </c>
-      <c r="F42" s="6">
-        <v>0.53926308253364341</v>
-      </c>
-      <c r="G42" s="6">
-        <v>0.22453964436855323</v>
-      </c>
-      <c r="H42" s="6">
-        <v>-0.23351403992684439</v>
-      </c>
-      <c r="I42" s="6">
-        <v>-9.4410666611589561E-2</v>
-      </c>
-      <c r="J42" s="6">
-        <v>-4.981323021222106E-2</v>
-      </c>
-      <c r="K42" s="6">
-        <v>-0.10380876831768313</v>
-      </c>
-      <c r="L42" s="6">
-        <v>18</v>
+      <c r="A42" s="6">
+        <v>1</v>
+      </c>
+      <c r="B42" s="7">
+        <v>0.61728376671648244</v>
+      </c>
+      <c r="C42" s="7">
+        <v>-0.76902066788280932</v>
+      </c>
+      <c r="D42" s="7">
+        <v>0.30629533473189952</v>
+      </c>
+      <c r="E42" s="7">
+        <v>0.75938344980842765</v>
+      </c>
+      <c r="F42" s="7">
+        <v>0.71391276211547494</v>
+      </c>
+      <c r="G42" s="7">
+        <v>0.33577463172092098</v>
+      </c>
+      <c r="H42" s="7">
+        <v>-0.22817724450063639</v>
+      </c>
+      <c r="I42" s="7">
+        <v>-0.62892559498955347</v>
+      </c>
+      <c r="J42" s="7">
+        <v>-0.45477578344153907</v>
+      </c>
+      <c r="K42" s="7">
+        <v>-0.52412395088768349</v>
+      </c>
+      <c r="L42" s="7">
+        <v>3</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A43" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="B43" s="6">
-        <v>0.39260850281133325</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-8.3071738573030227E-2</v>
-      </c>
-      <c r="D43" s="6">
-        <v>0.24964721058275932</v>
-      </c>
-      <c r="E43" s="6">
-        <v>0.47679042575026126</v>
-      </c>
-      <c r="F43" s="6">
-        <v>0.48707266570092295</v>
-      </c>
-      <c r="G43" s="6">
-        <v>0.21954689767454627</v>
-      </c>
-      <c r="H43" s="6">
-        <v>-5.5288962671237861E-2</v>
-      </c>
-      <c r="I43" s="6">
-        <v>-0.11495309722722752</v>
-      </c>
-      <c r="J43" s="6">
-        <v>2.2515718230161602E-2</v>
-      </c>
-      <c r="K43" s="6">
-        <v>-0.10166223966007563</v>
-      </c>
-      <c r="L43" s="6">
+      <c r="A43" s="6">
+        <v>2</v>
+      </c>
+      <c r="B43" s="7">
+        <v>0.42508940217000785</v>
+      </c>
+      <c r="C43" s="7">
+        <v>-0.10192509584711851</v>
+      </c>
+      <c r="D43" s="7">
+        <v>0.33071273032011239</v>
+      </c>
+      <c r="E43" s="7">
+        <v>0.45862718368684702</v>
+      </c>
+      <c r="F43" s="7">
+        <v>0.39849537778334221</v>
+      </c>
+      <c r="G43" s="7">
+        <v>0.12113788978529753</v>
+      </c>
+      <c r="H43" s="7">
+        <v>-0.20280745208169496</v>
+      </c>
+      <c r="I43" s="7">
+        <v>1.5420036073287227E-2</v>
+      </c>
+      <c r="J43" s="7">
+        <v>1.7235711700300842E-2</v>
+      </c>
+      <c r="K43" s="7">
+        <v>2.7662953769531651E-2</v>
+      </c>
+      <c r="L43" s="7">
         <v>3</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A44" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="B44" s="6">
-        <v>0.5082525680977753</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-0.52292651857862715</v>
-      </c>
-      <c r="D44" s="6">
-        <v>0.72292292445950623</v>
-      </c>
-      <c r="E44" s="6">
-        <v>0.52100496292045617</v>
-      </c>
-      <c r="F44" s="6">
-        <v>0.46332661514839257</v>
-      </c>
-      <c r="G44" s="6">
-        <v>0.12032099667413998</v>
-      </c>
-      <c r="H44" s="6">
-        <v>-1.3967237071352363</v>
-      </c>
-      <c r="I44" s="6">
-        <v>-6.3654471439531818E-2</v>
-      </c>
-      <c r="J44" s="6">
-        <v>-7.0746537102120794E-3</v>
-      </c>
-      <c r="K44" s="6">
-        <v>1.0526930614285892E-2</v>
-      </c>
-      <c r="L44" s="6">
-        <v>3</v>
+      <c r="A44" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B44" s="7">
+        <v>0.51831274327671839</v>
+      </c>
+      <c r="C44" s="7">
+        <v>-1.4714459639019677E-2</v>
+      </c>
+      <c r="D44" s="7">
+        <v>0.1754951995061842</v>
+      </c>
+      <c r="E44" s="7">
+        <v>0.76432342191514846</v>
+      </c>
+      <c r="F44" s="7">
+        <v>0.70385573609834662</v>
+      </c>
+      <c r="G44" s="7">
+        <v>0.38670415294970145</v>
+      </c>
+      <c r="H44" s="7">
+        <v>7.8718019639362369E-2</v>
+      </c>
+      <c r="I44" s="7">
+        <v>-8.2295858147006379E-2</v>
+      </c>
+      <c r="J44" s="7">
+        <v>-2.7148222120558846E-3</v>
+      </c>
+      <c r="K44" s="7">
+        <v>-0.11113866381187298</v>
+      </c>
+      <c r="L44" s="7">
+        <v>18</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A45" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="B45" s="6">
-        <v>0.53216326702162431</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-0.16760771138593752</v>
-      </c>
-      <c r="D45" s="6">
-        <v>8.8240536646411405E-2</v>
-      </c>
-      <c r="E45" s="6">
-        <v>0.81102169526578083</v>
-      </c>
-      <c r="F45" s="6">
-        <v>0.76208612282829591</v>
-      </c>
-      <c r="G45" s="6">
-        <v>0.35758988016334398</v>
-      </c>
-      <c r="H45" s="6">
-        <v>0.10097006434570682</v>
-      </c>
-      <c r="I45" s="6">
-        <v>-0.19798276297227824</v>
-      </c>
-      <c r="J45" s="6">
-        <v>-0.21420359885862469</v>
-      </c>
-      <c r="K45" s="6">
-        <v>-0.35543535699188977</v>
-      </c>
-      <c r="L45" s="6">
-        <v>3</v>
+      <c r="A45" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B45" s="7">
+        <v>0.5601308434124237</v>
+      </c>
+      <c r="C45" s="7">
+        <v>7.5447093290681458E-2</v>
+      </c>
+      <c r="D45" s="7">
+        <v>0.25000153870036373</v>
+      </c>
+      <c r="E45" s="7">
+        <v>0.77496668540107805</v>
+      </c>
+      <c r="F45" s="7">
+        <v>0.75339251864007373</v>
+      </c>
+      <c r="G45" s="7">
+        <v>0.42159475431731658</v>
+      </c>
+      <c r="H45" s="7">
+        <v>6.7610520723654463E-2</v>
+      </c>
+      <c r="I45" s="7">
+        <v>7.2570994868530053E-2</v>
+      </c>
+      <c r="J45" s="7">
+        <v>7.7880977995827147E-2</v>
+      </c>
+      <c r="K45" s="7">
+        <v>-9.3969243136080058E-2</v>
+      </c>
+      <c r="L45" s="7">
+        <v>6</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A46" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="B46" s="6">
-        <v>0.42508940217000785</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-0.10192509584711851</v>
-      </c>
-      <c r="D46" s="6">
-        <v>0.33071273032011239</v>
-      </c>
-      <c r="E46" s="6">
-        <v>0.45862718368684702</v>
-      </c>
-      <c r="F46" s="6">
-        <v>0.39849537778334221</v>
-      </c>
-      <c r="G46" s="6">
-        <v>0.12113788978529753</v>
-      </c>
-      <c r="H46" s="6">
-        <v>-0.20280745208169496</v>
-      </c>
-      <c r="I46" s="6">
-        <v>1.5420036073287227E-2</v>
-      </c>
-      <c r="J46" s="6">
-        <v>1.7235711700300842E-2</v>
-      </c>
-      <c r="K46" s="6">
-        <v>2.7662953769531651E-2</v>
-      </c>
-      <c r="L46" s="6">
+      <c r="A46" s="6">
+        <v>1</v>
+      </c>
+      <c r="B46" s="7">
+        <v>0.6138157437778643</v>
+      </c>
+      <c r="C46" s="7">
+        <v>-3.4862205004359361E-3</v>
+      </c>
+      <c r="D46" s="7">
+        <v>0.16922130705442448</v>
+      </c>
+      <c r="E46" s="7">
+        <v>0.81835098263436146</v>
+      </c>
+      <c r="F46" s="7">
+        <v>0.78534528081842669</v>
+      </c>
+      <c r="G46" s="7">
+        <v>0.63761387382735257</v>
+      </c>
+      <c r="H46" s="7">
+        <v>-2.3778768328583045E-2</v>
+      </c>
+      <c r="I46" s="7">
+        <v>-3.2207113447426022E-2</v>
+      </c>
+      <c r="J46" s="7">
+        <v>1.1624500593604351E-2</v>
+      </c>
+      <c r="K46" s="7">
+        <v>-0.21691001356242637</v>
+      </c>
+      <c r="L46" s="7">
         <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A47" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="B47" s="6">
-        <v>0.483441348099793</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-4.0490433240804438E-2</v>
-      </c>
-      <c r="D47" s="6">
-        <v>0.27300596143393557</v>
-      </c>
-      <c r="E47" s="6">
-        <v>0.66927613696360255</v>
-      </c>
-      <c r="F47" s="6">
-        <v>0.59551391906913631</v>
-      </c>
-      <c r="G47" s="6">
-        <v>0.35134226410219749</v>
-      </c>
-      <c r="H47" s="6">
-        <v>0.10432618658787619</v>
-      </c>
-      <c r="I47" s="6">
-        <v>1.9489168401389135E-2</v>
-      </c>
-      <c r="J47" s="6">
-        <v>1.5319526625009497E-2</v>
-      </c>
-      <c r="K47" s="6">
-        <v>-0.17081497689756256</v>
-      </c>
-      <c r="L47" s="6">
+      <c r="A47" s="6">
+        <v>2</v>
+      </c>
+      <c r="B47" s="7">
+        <v>0.5064459430469832</v>
+      </c>
+      <c r="C47" s="7">
+        <v>0.15438040708179887</v>
+      </c>
+      <c r="D47" s="7">
+        <v>0.33078177034630302</v>
+      </c>
+      <c r="E47" s="7">
+        <v>0.73158238816779464</v>
+      </c>
+      <c r="F47" s="7">
+        <v>0.72143975646172065</v>
+      </c>
+      <c r="G47" s="7">
+        <v>0.2055756348072805</v>
+      </c>
+      <c r="H47" s="7">
+        <v>0.15899980977589198</v>
+      </c>
+      <c r="I47" s="7">
+        <v>0.17734910318448613</v>
+      </c>
+      <c r="J47" s="7">
+        <v>0.14413745539804992</v>
+      </c>
+      <c r="K47" s="7">
+        <v>2.897152729026627E-2</v>
+      </c>
+      <c r="L47" s="7">
         <v>3</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A48" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="B48" s="6">
-        <v>0.40264009063046097</v>
-      </c>
-      <c r="C48" s="6">
-        <v>-7.5603949708111434E-2</v>
-      </c>
-      <c r="D48" s="6">
-        <v>0.31818130724981031</v>
-      </c>
-      <c r="E48" s="6">
-        <v>0.50388591293620022</v>
-      </c>
-      <c r="F48" s="6">
-        <v>0.52908379467177125</v>
-      </c>
-      <c r="G48" s="6">
-        <v>0.17729993781179376</v>
-      </c>
-      <c r="H48" s="6">
-        <v>4.843963139352029E-2</v>
-      </c>
-      <c r="I48" s="6">
-        <v>-0.22478287250517623</v>
-      </c>
-      <c r="J48" s="6">
-        <v>-0.13267208525996158</v>
-      </c>
-      <c r="K48" s="6">
-        <v>-3.3129920740388341E-2</v>
-      </c>
-      <c r="L48" s="6">
-        <v>3</v>
+      <c r="A48" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B48" s="7">
+        <v>0.51560716945070195</v>
+      </c>
+      <c r="C48" s="7">
+        <v>-1.8943057246910543E-2</v>
+      </c>
+      <c r="D48" s="7">
+        <v>0.13005486076672015</v>
+      </c>
+      <c r="E48" s="7">
+        <v>0.80693315314510672</v>
+      </c>
+      <c r="F48" s="7">
+        <v>0.70838710624479229</v>
+      </c>
+      <c r="G48" s="7">
+        <v>0.36247944190169884</v>
+      </c>
+      <c r="H48" s="7">
+        <v>9.5116178249819106E-2</v>
+      </c>
+      <c r="I48" s="7">
+        <v>-0.10841000750147917</v>
+      </c>
+      <c r="J48" s="7">
+        <v>-9.1261657539539756E-2</v>
+      </c>
+      <c r="K48" s="7">
+        <v>-3.9917016526826311E-2</v>
+      </c>
+      <c r="L48" s="7">
+        <v>6</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A49" s="4" t="s">
+      <c r="A49" s="6">
+        <v>1</v>
+      </c>
+      <c r="B49" s="7">
+        <v>0.55260196350000446</v>
+      </c>
+      <c r="C49" s="7">
+        <v>8.6096849761306923E-2</v>
+      </c>
+      <c r="D49" s="7">
+        <v>9.2256390976537261E-2</v>
+      </c>
+      <c r="E49" s="7">
+        <v>0.81968169121487156</v>
+      </c>
+      <c r="F49" s="7">
+        <v>0.74776498923801249</v>
+      </c>
+      <c r="G49" s="7">
+        <v>0.47306152227834614</v>
+      </c>
+      <c r="H49" s="7">
+        <v>4.1738881638607672E-2</v>
+      </c>
+      <c r="I49" s="7">
+        <v>1.4359642655774635E-2</v>
+      </c>
+      <c r="J49" s="7">
+        <v>0.12750077329609397</v>
+      </c>
+      <c r="K49" s="7">
+        <v>-3.3430254747818938E-2</v>
+      </c>
+      <c r="L49" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A50" s="6">
+        <v>2</v>
+      </c>
+      <c r="B50" s="7">
+        <v>0.4786123754013995</v>
+      </c>
+      <c r="C50" s="7">
+        <v>-0.123982964255128</v>
+      </c>
+      <c r="D50" s="7">
+        <v>0.16785333055690307</v>
+      </c>
+      <c r="E50" s="7">
+        <v>0.79418461507534188</v>
+      </c>
+      <c r="F50" s="7">
+        <v>0.66900922325157242</v>
+      </c>
+      <c r="G50" s="7">
+        <v>0.25189736152505154</v>
+      </c>
+      <c r="H50" s="7">
+        <v>0.14849347486103057</v>
+      </c>
+      <c r="I50" s="7">
+        <v>-0.23117965765873297</v>
+      </c>
+      <c r="J50" s="7">
+        <v>-0.31002408837517348</v>
+      </c>
+      <c r="K50" s="7">
+        <v>-4.6403778305833678E-2</v>
+      </c>
+      <c r="L50" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A51" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B51" s="7">
+        <v>0.47920021696702975</v>
+      </c>
+      <c r="C51" s="7">
+        <v>-0.10064741496082996</v>
+      </c>
+      <c r="D51" s="7">
+        <v>0.1464291990514687</v>
+      </c>
+      <c r="E51" s="7">
+        <v>0.71107042719926028</v>
+      </c>
+      <c r="F51" s="7">
+        <v>0.64978758341017306</v>
+      </c>
+      <c r="G51" s="7">
+        <v>0.37603826263008894</v>
+      </c>
+      <c r="H51" s="7">
+        <v>7.3427359944613579E-2</v>
+      </c>
+      <c r="I51" s="7">
+        <v>-0.21104856180807</v>
+      </c>
+      <c r="J51" s="7">
+        <v>5.2362129075449642E-3</v>
+      </c>
+      <c r="K51" s="7">
+        <v>-0.19952973177271258</v>
+      </c>
+      <c r="L51" s="7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A52" s="6">
+        <v>1</v>
+      </c>
+      <c r="B52" s="7">
+        <v>0.47495908583426649</v>
+      </c>
+      <c r="C52" s="7">
+        <v>-0.16080439668085547</v>
+      </c>
+      <c r="D52" s="7">
+        <v>1.9852436669001865E-2</v>
+      </c>
+      <c r="E52" s="7">
+        <v>0.7528647174349179</v>
+      </c>
+      <c r="F52" s="7">
+        <v>0.70406124775120971</v>
+      </c>
+      <c r="G52" s="7">
+        <v>0.40073426115798055</v>
+      </c>
+      <c r="H52" s="7">
+        <v>4.2528533301350951E-2</v>
+      </c>
+      <c r="I52" s="7">
+        <v>-0.44158629201752914</v>
+      </c>
+      <c r="J52" s="7">
+        <v>-4.8471008099195689E-3</v>
+      </c>
+      <c r="K52" s="7">
+        <v>-0.22824448664786257</v>
+      </c>
+      <c r="L52" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A53" s="6">
+        <v>2</v>
+      </c>
+      <c r="B53" s="7">
+        <v>0.483441348099793</v>
+      </c>
+      <c r="C53" s="7">
+        <v>-4.0490433240804438E-2</v>
+      </c>
+      <c r="D53" s="7">
+        <v>0.27300596143393557</v>
+      </c>
+      <c r="E53" s="7">
+        <v>0.66927613696360255</v>
+      </c>
+      <c r="F53" s="7">
+        <v>0.59551391906913631</v>
+      </c>
+      <c r="G53" s="7">
+        <v>0.35134226410219749</v>
+      </c>
+      <c r="H53" s="7">
+        <v>0.10432618658787619</v>
+      </c>
+      <c r="I53" s="7">
+        <v>1.9489168401389135E-2</v>
+      </c>
+      <c r="J53" s="7">
+        <v>1.5319526625009497E-2</v>
+      </c>
+      <c r="K53" s="7">
+        <v>-0.17081497689756256</v>
+      </c>
+      <c r="L53" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A54" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B54" s="7">
+        <v>0.43740971611575158</v>
+      </c>
+      <c r="C54" s="7">
+        <v>0.14132109084805186</v>
+      </c>
+      <c r="D54" s="7">
+        <v>0.35404140292494768</v>
+      </c>
+      <c r="E54" s="7">
+        <v>0.57600547372663358</v>
+      </c>
+      <c r="F54" s="7">
+        <v>0.66510574467229067</v>
+      </c>
+      <c r="G54" s="7">
+        <v>0.13065370834142198</v>
+      </c>
+      <c r="H54" s="7">
+        <v>-0.11906420689696035</v>
+      </c>
+      <c r="I54" s="7">
+        <v>0.28151544116557842</v>
+      </c>
+      <c r="J54" s="7">
+        <v>0.39233368945831237</v>
+      </c>
+      <c r="K54" s="7">
+        <v>3.3216971587337082E-3</v>
+      </c>
+      <c r="L54" s="7">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A55" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B55" s="7">
+        <v>0.51653299765072724</v>
+      </c>
+      <c r="C55" s="7">
+        <v>0.25452422776537131</v>
+      </c>
+      <c r="D55" s="7">
+        <v>0.38641688657473017</v>
+      </c>
+      <c r="E55" s="7">
+        <v>0.69438217238658384</v>
+      </c>
+      <c r="F55" s="7">
+        <v>0.78766274978572393</v>
+      </c>
+      <c r="G55" s="7">
+        <v>0.14344970039779883</v>
+      </c>
+      <c r="H55" s="7">
+        <v>-0.1287801191866593</v>
+      </c>
+      <c r="I55" s="7">
+        <v>0.51722298549684764</v>
+      </c>
+      <c r="J55" s="7">
+        <v>0.58069840693139196</v>
+      </c>
+      <c r="K55" s="7">
+        <v>2.2986249696157295E-2</v>
+      </c>
+      <c r="L55" s="7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A56" s="6">
+        <v>1</v>
+      </c>
+      <c r="B56" s="7">
+        <v>0.51089315786734568</v>
+      </c>
+      <c r="C56" s="7">
+        <v>0.31613870598685806</v>
+      </c>
+      <c r="D56" s="7">
+        <v>0.28381595113495078</v>
+      </c>
+      <c r="E56" s="7">
+        <v>0.69934830734722297</v>
+      </c>
+      <c r="F56" s="7">
+        <v>0.83227867361021912</v>
+      </c>
+      <c r="G56" s="7">
+        <v>0.16816237476339291</v>
+      </c>
+      <c r="H56" s="7">
+        <v>-0.27615557348357217</v>
+      </c>
+      <c r="I56" s="7">
+        <v>0.68962093642462452</v>
+      </c>
+      <c r="J56" s="7">
+        <v>0.8085982772193514</v>
+      </c>
+      <c r="K56" s="7">
+        <v>2.7451850015895157E-2</v>
+      </c>
+      <c r="L56" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A57" s="6">
+        <v>2</v>
+      </c>
+      <c r="B57" s="7">
+        <v>0.52217283743410892</v>
+      </c>
+      <c r="C57" s="7">
+        <v>0.1929097495438846</v>
+      </c>
+      <c r="D57" s="7">
+        <v>0.48901782201450961</v>
+      </c>
+      <c r="E57" s="7">
+        <v>0.68941603742594493</v>
+      </c>
+      <c r="F57" s="7">
+        <v>0.74304682596122873</v>
+      </c>
+      <c r="G57" s="7">
+        <v>0.11873702603220478</v>
+      </c>
+      <c r="H57" s="7">
+        <v>1.8595335110253564E-2</v>
+      </c>
+      <c r="I57" s="7">
+        <v>0.34482503456907088</v>
+      </c>
+      <c r="J57" s="7">
+        <v>0.35279853664343247</v>
+      </c>
+      <c r="K57" s="7">
+        <v>1.8520649376419434E-2</v>
+      </c>
+      <c r="L57" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A58" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B58" s="7">
+        <v>0.4107712263729606</v>
+      </c>
+      <c r="C58" s="7">
+        <v>0.1025180715015888</v>
+      </c>
+      <c r="D58" s="7">
+        <v>0.33772107419067016</v>
+      </c>
+      <c r="E58" s="7">
+        <v>0.57069592110497291</v>
+      </c>
+      <c r="F58" s="7">
+        <v>0.64812887859284618</v>
+      </c>
+      <c r="G58" s="7">
+        <v>0.1055553089493142</v>
+      </c>
+      <c r="H58" s="7">
+        <v>-9.6441530814164414E-2</v>
+      </c>
+      <c r="I58" s="7">
+        <v>0.24968918083729844</v>
+      </c>
+      <c r="J58" s="7">
+        <v>0.34404482638119066</v>
+      </c>
+      <c r="K58" s="7">
+        <v>-4.1257583762440216E-2</v>
+      </c>
+      <c r="L58" s="7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A59" s="6">
+        <v>1</v>
+      </c>
+      <c r="B59" s="7">
+        <v>0.44159419412147088</v>
+      </c>
+      <c r="C59" s="7">
+        <v>0.28743008411231286</v>
+      </c>
+      <c r="D59" s="7">
+        <v>0.30466336353257728</v>
+      </c>
+      <c r="E59" s="7">
+        <v>0.62815750637619383</v>
+      </c>
+      <c r="F59" s="7">
+        <v>0.73208768374144262</v>
+      </c>
+      <c r="G59" s="7">
+        <v>0.10764524266119437</v>
+      </c>
+      <c r="H59" s="7">
+        <v>-0.2265754064982485</v>
+      </c>
+      <c r="I59" s="7">
+        <v>0.67226067232492459</v>
+      </c>
+      <c r="J59" s="7">
+        <v>0.77753120562933453</v>
+      </c>
+      <c r="K59" s="7">
+        <v>-1.0945093202310654E-3</v>
+      </c>
+      <c r="L59" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A60" s="6">
+        <v>2</v>
+      </c>
+      <c r="B60" s="7">
+        <v>0.37994825862445031</v>
+      </c>
+      <c r="C60" s="7">
+        <v>-8.2393941109135269E-2</v>
+      </c>
+      <c r="D60" s="7">
+        <v>0.37077878484876309</v>
+      </c>
+      <c r="E60" s="7">
+        <v>0.513234335833752</v>
+      </c>
+      <c r="F60" s="7">
+        <v>0.56417007344424963</v>
+      </c>
+      <c r="G60" s="7">
+        <v>0.10346537523743403</v>
+      </c>
+      <c r="H60" s="7">
+        <v>3.3692344869919677E-2</v>
+      </c>
+      <c r="I60" s="7">
+        <v>-0.17288231065032766</v>
+      </c>
+      <c r="J60" s="7">
+        <v>-8.9441552866953211E-2</v>
+      </c>
+      <c r="K60" s="7">
+        <v>-8.1420658204649374E-2</v>
+      </c>
+      <c r="L60" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A61" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B61" s="7">
+        <v>0.38492492432356668</v>
+      </c>
+      <c r="C61" s="7">
+        <v>6.6920973277195359E-2</v>
+      </c>
+      <c r="D61" s="7">
+        <v>0.33798624800944294</v>
+      </c>
+      <c r="E61" s="7">
+        <v>0.4629383276883437</v>
+      </c>
+      <c r="F61" s="7">
+        <v>0.55952560563830211</v>
+      </c>
+      <c r="G61" s="7">
+        <v>0.14295611567715291</v>
+      </c>
+      <c r="H61" s="7">
+        <v>-0.13197097069005723</v>
+      </c>
+      <c r="I61" s="7">
+        <v>7.7634157162589215E-2</v>
+      </c>
+      <c r="J61" s="7">
+        <v>0.2522578350623545</v>
+      </c>
+      <c r="K61" s="7">
+        <v>2.823642554248405E-2</v>
+      </c>
+      <c r="L61" s="7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A62" s="6">
+        <v>1</v>
+      </c>
+      <c r="B62" s="7">
+        <v>0.36720975801667244</v>
+      </c>
+      <c r="C62" s="7">
+        <v>0.20944589626250218</v>
+      </c>
+      <c r="D62" s="7">
+        <v>0.35779118876907551</v>
+      </c>
+      <c r="E62" s="7">
+        <v>0.42199074244048734</v>
+      </c>
+      <c r="F62" s="7">
+        <v>0.58996741660483298</v>
+      </c>
+      <c r="G62" s="7">
+        <v>0.10861229354251208</v>
+      </c>
+      <c r="H62" s="7">
+        <v>-0.31238157277363476</v>
+      </c>
+      <c r="I62" s="7">
+        <v>0.38005118683035466</v>
+      </c>
+      <c r="J62" s="7">
+        <v>0.63718775538467065</v>
+      </c>
+      <c r="K62" s="7">
+        <v>8.9602771825356434E-2</v>
+      </c>
+      <c r="L62" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A63" s="6">
+        <v>2</v>
+      </c>
+      <c r="B63" s="7">
+        <v>0.40264009063046097</v>
+      </c>
+      <c r="C63" s="7">
+        <v>-7.5603949708111434E-2</v>
+      </c>
+      <c r="D63" s="7">
+        <v>0.31818130724981031</v>
+      </c>
+      <c r="E63" s="7">
+        <v>0.50388591293620022</v>
+      </c>
+      <c r="F63" s="7">
+        <v>0.52908379467177125</v>
+      </c>
+      <c r="G63" s="7">
+        <v>0.17729993781179376</v>
+      </c>
+      <c r="H63" s="7">
+        <v>4.843963139352029E-2</v>
+      </c>
+      <c r="I63" s="7">
+        <v>-0.22478287250517623</v>
+      </c>
+      <c r="J63" s="7">
+        <v>-0.13267208525996158</v>
+      </c>
+      <c r="K63" s="7">
+        <v>-3.3129920740388341E-2</v>
+      </c>
+      <c r="L63" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A64" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="B49" s="6">
-        <v>0.48038761352538967</v>
-      </c>
-      <c r="C49" s="6">
-        <v>-9.2899865713453086E-2</v>
-      </c>
-      <c r="D49" s="6">
-        <v>0.32353551655531937</v>
-      </c>
-      <c r="E49" s="6">
-        <v>0.5993512792659248</v>
-      </c>
-      <c r="F49" s="6">
-        <v>0.58270419240173066</v>
-      </c>
-      <c r="G49" s="6">
-        <v>0.29683109460903612</v>
-      </c>
-      <c r="H49" s="6">
-        <v>-0.17915624404180225</v>
-      </c>
-      <c r="I49" s="6">
-        <v>2.2404894928493087E-3</v>
-      </c>
-      <c r="J49" s="6">
-        <v>7.9613468041370192E-2</v>
-      </c>
-      <c r="K49" s="6">
-        <v>-0.11221762652978086</v>
-      </c>
-      <c r="L49" s="6">
+      <c r="B64" s="7">
+        <v>0.48038761352538972</v>
+      </c>
+      <c r="C64" s="7">
+        <v>-9.2899865713453156E-2</v>
+      </c>
+      <c r="D64" s="7">
+        <v>0.32353551655531959</v>
+      </c>
+      <c r="E64" s="7">
+        <v>0.59935127926592469</v>
+      </c>
+      <c r="F64" s="7">
+        <v>0.58270419240173077</v>
+      </c>
+      <c r="G64" s="7">
+        <v>0.29683109460903601</v>
+      </c>
+      <c r="H64" s="7">
+        <v>-0.17915624404180217</v>
+      </c>
+      <c r="I64" s="7">
+        <v>2.240489492849294E-3</v>
+      </c>
+      <c r="J64" s="7">
+        <v>7.9613468041370206E-2</v>
+      </c>
+      <c r="K64" s="7">
+        <v>-0.1122176265297809</v>
+      </c>
+      <c r="L64" s="7">
         <v>108</v>
       </c>
     </row>

--- a/logs/one_head_map_search_optimization/one_head_map_search_optimization.xlsx
+++ b/logs/one_head_map_search_optimization/one_head_map_search_optimization.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgep-my.sharepoint.com/personal/uxue_ballarin_alumni_mondragon_edu/Documents/Semestre 8-Erasmus/Simula/ship_qnn/logs/one_head_map_search_optimization/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="116" documentId="11_AD4D2F04E46CFB4ACB3E20D455D6CCDA693EDF1F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3558DBD7-2E40-4DCE-AAAB-92D53675D2D6}"/>
+  <xr:revisionPtr revIDLastSave="125" documentId="11_AD4D2F04E46CFB4ACB3E20D455D6CCDA693EDF1F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{408F4DBE-D1D6-4CD8-896B-A34C9F48B934}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-5580" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId3"/>
+    <pivotCache cacheId="3" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1000,13 +1000,19 @@
       <sharedItems/>
     </cacheField>
     <cacheField name="head_number" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="1"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="1" count="1">
+        <n v="1"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="encoding" numFmtId="0">
-      <sharedItems/>
+      <sharedItems count="1">
+        <s v="serial"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="ansatz" numFmtId="0">
-      <sharedItems/>
+      <sharedItems count="1">
+        <s v="effsu2"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="entangle" numFmtId="0">
       <sharedItems count="3">
@@ -1216,9 +1222,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [-1, 2, 4, 0, 3, 1]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="0"/>
@@ -1293,9 +1299,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [-1, 0, 1, 2, 3, 4]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="1"/>
     <x v="0"/>
     <x v="1"/>
@@ -1370,9 +1376,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'rev', 'map': [-1, 2, 4, 0, 3, 1]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="2"/>
     <x v="0"/>
     <x v="0"/>
@@ -1447,9 +1453,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [-1, 0, 1, 2, 3, 4]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="1"/>
@@ -1524,9 +1530,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [-1, 0, 1, 2, 3, 4]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="1"/>
@@ -1601,9 +1607,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [-1, 0, 1, 2, 3, 4]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="1"/>
@@ -1678,9 +1684,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'rev', 'map': [-1, 0, 1, 2, 3, 4]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="2"/>
     <x v="0"/>
     <x v="1"/>
@@ -1755,9 +1761,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [-1, 0, 1, 2, 3, 4]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="1"/>
     <x v="0"/>
     <x v="1"/>
@@ -1832,9 +1838,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [-1, 2, 4, 0, 3, 1]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="0"/>
@@ -1909,9 +1915,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'rev', 'map': [0, 1, -1, 2, 3, 4]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="2"/>
     <x v="0"/>
     <x v="2"/>
@@ -1986,9 +1992,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'rev', 'map': [-1, 2, 4, 0, 3, 1]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="2"/>
     <x v="0"/>
     <x v="0"/>
@@ -2063,9 +2069,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'rev', 'map': [0, 1, -1, 2, 3, 4]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="2"/>
     <x v="0"/>
     <x v="2"/>
@@ -2140,9 +2146,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [-1, 2, 4, 0, 3, 1]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="1"/>
     <x v="0"/>
     <x v="0"/>
@@ -2217,9 +2223,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, -1, 2, 3, 4]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="2"/>
@@ -2294,9 +2300,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [1, 3, 0, 4, 2, -1]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="1"/>
     <x v="0"/>
     <x v="3"/>
@@ -2371,9 +2377,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [1, 3, 0, 4, 2, -1]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="1"/>
     <x v="0"/>
     <x v="3"/>
@@ -2448,9 +2454,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'rev', 'map': [0, 1, -1, 2, 3, 4]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="2"/>
     <x v="0"/>
     <x v="2"/>
@@ -2525,9 +2531,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1, 2, 3, 4]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="1"/>
     <x v="0"/>
     <x v="2"/>
@@ -2602,9 +2608,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'rev', 'map': [-1, 2, 4, 0, 3, 1]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="2"/>
     <x v="0"/>
     <x v="0"/>
@@ -2679,9 +2685,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [4, 2, -1, 0, 3, 1]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="4"/>
@@ -2756,9 +2762,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [-1, 2, 4, 0, 3, 1]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="1"/>
     <x v="0"/>
     <x v="0"/>
@@ -2833,9 +2839,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [-1, 2, 4, 0, 3, 1]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="0"/>
@@ -2910,9 +2916,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1, 2, 3, 4]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="1"/>
     <x v="0"/>
     <x v="2"/>
@@ -2987,9 +2993,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [4, 2, -1, 0, 3, 1]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="4"/>
@@ -3064,9 +3070,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [4, 2, -1, 0, 3, 1]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="4"/>
@@ -3141,9 +3147,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'rev', 'map': [1, 3, 0, 4, 2, -1]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="2"/>
     <x v="0"/>
     <x v="3"/>
@@ -3218,9 +3224,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'rev', 'map': [1, 3, 0, 4, 2, -1]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="2"/>
     <x v="0"/>
     <x v="3"/>
@@ -3295,9 +3301,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 3, 1, -1, 4, 2]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="5"/>
@@ -3372,9 +3378,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1, 2, 3, 4]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="1"/>
     <x v="0"/>
     <x v="2"/>
@@ -3449,9 +3455,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [-1, 2, 4, 0, 3, 1]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="1"/>
     <x v="0"/>
     <x v="0"/>
@@ -3526,9 +3532,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [4, 2, -1, 0, 3, 1]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="1"/>
     <x v="0"/>
     <x v="4"/>
@@ -3603,9 +3609,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'rev', 'map': [1, 3, 0, 4, 2, -1]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="2"/>
     <x v="0"/>
     <x v="3"/>
@@ -3680,9 +3686,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, -1, 2, 3, 4]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="2"/>
@@ -3757,9 +3763,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [4, 2, -1, 0, 3, 1]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="1"/>
     <x v="0"/>
     <x v="4"/>
@@ -3834,9 +3840,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 3, 1, -1, 4, 2]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="5"/>
@@ -3911,9 +3917,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [4, 2, -1, 0, 3, 1]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="1"/>
     <x v="0"/>
     <x v="4"/>
@@ -3988,9 +3994,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'rev', 'map': [4, 2, -1, 0, 3, 1]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="2"/>
     <x v="0"/>
     <x v="4"/>
@@ -4065,9 +4071,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, -1, 2, 3, 4]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="2"/>
@@ -4142,9 +4148,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'rev', 'map': [4, 2, -1, 0, 3, 1]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="2"/>
     <x v="0"/>
     <x v="4"/>
@@ -4219,9 +4225,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'rev', 'map': [4, 2, -1, 0, 3, 1]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="2"/>
     <x v="0"/>
     <x v="4"/>
@@ -4296,9 +4302,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 3, 1, -1, 4, 2]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="1"/>
     <x v="0"/>
     <x v="5"/>
@@ -4373,9 +4379,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 3, 1, -1, 4, 2]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="1"/>
     <x v="0"/>
     <x v="5"/>
@@ -4450,9 +4456,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'rev', 'map': [0, 3, 1, -1, 4, 2]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="2"/>
     <x v="0"/>
     <x v="5"/>
@@ -4527,9 +4533,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 3, 1, -1, 4, 2]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="1"/>
     <x v="0"/>
     <x v="5"/>
@@ -4604,9 +4610,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'rev', 'map': [0, 3, 1, -1, 4, 2]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="2"/>
     <x v="0"/>
     <x v="5"/>
@@ -4681,9 +4687,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'rev', 'map': [0, 3, 1, -1, 4, 2]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="2"/>
     <x v="0"/>
     <x v="5"/>
@@ -4758,9 +4764,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 3, 1, -1, 4, 2]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="5"/>
@@ -4835,9 +4841,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [1, 3, 0, 4, 2, -1]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="1"/>
     <x v="0"/>
     <x v="3"/>
@@ -4912,9 +4918,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [1, 3, 0, 4, 2, -1]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="3"/>
@@ -4989,9 +4995,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'rev', 'map': [-1, 0, 1, 2, 3, 4]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="2"/>
     <x v="1"/>
     <x v="1"/>
@@ -5066,9 +5072,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [1, 3, 0, 4, 2, -1]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="3"/>
@@ -5143,9 +5149,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [-1, 0, 1, 2, 3, 4]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="1"/>
     <x v="1"/>
     <x v="1"/>
@@ -5220,9 +5226,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'rev', 'map': [-1, 0, 1, 2, 3, 4]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="2"/>
     <x v="1"/>
     <x v="1"/>
@@ -5297,9 +5303,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [1, 3, 0, 4, 2, -1]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="3"/>
@@ -5374,9 +5380,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [-1, 0, 1, 2, 3, 4]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="1"/>
     <x v="1"/>
     <x v="1"/>
@@ -5451,9 +5457,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'rev', 'map': [-1, 0, 1, 2, 3, 4]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="2"/>
     <x v="1"/>
     <x v="1"/>
@@ -5528,9 +5534,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [-1, 0, 1, 2, 3, 4]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="1"/>
     <x v="1"/>
@@ -5605,9 +5611,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [-1, 0, 1, 2, 3, 4]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="1"/>
     <x v="1"/>
     <x v="1"/>
@@ -5682,9 +5688,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'rev', 'map': [-1, 2, 4, 0, 3, 1]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="2"/>
     <x v="1"/>
     <x v="0"/>
@@ -5759,9 +5765,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [-1, 0, 1, 2, 3, 4]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="1"/>
     <x v="1"/>
@@ -5836,9 +5842,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [-1, 2, 4, 0, 3, 1]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="1"/>
     <x v="1"/>
     <x v="0"/>
@@ -5913,9 +5919,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'rev', 'map': [-1, 2, 4, 0, 3, 1]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="2"/>
     <x v="1"/>
     <x v="0"/>
@@ -5990,9 +5996,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [-1, 0, 1, 2, 3, 4]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="1"/>
     <x v="1"/>
@@ -6067,9 +6073,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [-1, 2, 4, 0, 3, 1]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="1"/>
     <x v="1"/>
     <x v="0"/>
@@ -6144,9 +6150,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'rev', 'map': [-1, 2, 4, 0, 3, 1]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="2"/>
     <x v="1"/>
     <x v="0"/>
@@ -6221,9 +6227,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [-1, 2, 4, 0, 3, 1]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="1"/>
     <x v="0"/>
@@ -6298,9 +6304,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [-1, 2, 4, 0, 3, 1]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="1"/>
     <x v="1"/>
     <x v="0"/>
@@ -6375,9 +6381,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'rev', 'map': [0, 1, -1, 2, 3, 4]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="2"/>
     <x v="1"/>
     <x v="2"/>
@@ -6452,9 +6458,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1, 2, 3, 4]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="1"/>
     <x v="1"/>
     <x v="2"/>
@@ -6529,9 +6535,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [-1, 2, 4, 0, 3, 1]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="1"/>
     <x v="0"/>
@@ -6606,9 +6612,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'rev', 'map': [0, 1, -1, 2, 3, 4]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="2"/>
     <x v="1"/>
     <x v="2"/>
@@ -6683,9 +6689,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1, 2, 3, 4]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="1"/>
     <x v="1"/>
     <x v="2"/>
@@ -6760,9 +6766,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [-1, 2, 4, 0, 3, 1]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="1"/>
     <x v="0"/>
@@ -6837,9 +6843,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'rev', 'map': [0, 1, -1, 2, 3, 4]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="2"/>
     <x v="1"/>
     <x v="2"/>
@@ -6914,9 +6920,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1, 2, 3, 4]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="1"/>
     <x v="1"/>
     <x v="2"/>
@@ -6991,9 +6997,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, -1, 2, 3, 4]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="1"/>
     <x v="2"/>
@@ -7068,9 +7074,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'rev', 'map': [4, 2, -1, 0, 3, 1]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="2"/>
     <x v="1"/>
     <x v="4"/>
@@ -7145,9 +7151,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [4, 2, -1, 0, 3, 1]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="1"/>
     <x v="1"/>
     <x v="4"/>
@@ -7222,9 +7228,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, -1, 2, 3, 4]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="1"/>
     <x v="2"/>
@@ -7299,9 +7305,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'rev', 'map': [4, 2, -1, 0, 3, 1]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="2"/>
     <x v="1"/>
     <x v="4"/>
@@ -7376,9 +7382,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [4, 2, -1, 0, 3, 1]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="1"/>
     <x v="1"/>
     <x v="4"/>
@@ -7453,9 +7459,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'rev', 'map': [4, 2, -1, 0, 3, 1]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="2"/>
     <x v="1"/>
     <x v="4"/>
@@ -7530,9 +7536,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, -1, 2, 3, 4]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="1"/>
     <x v="2"/>
@@ -7607,9 +7613,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [4, 2, -1, 0, 3, 1]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="1"/>
     <x v="1"/>
     <x v="4"/>
@@ -7684,9 +7690,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'rev', 'map': [0, 3, 1, -1, 4, 2]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="2"/>
     <x v="1"/>
     <x v="5"/>
@@ -7761,9 +7767,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [4, 2, -1, 0, 3, 1]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="1"/>
     <x v="4"/>
@@ -7838,9 +7844,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 3, 1, -1, 4, 2]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="1"/>
     <x v="1"/>
     <x v="5"/>
@@ -7915,9 +7921,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'rev', 'map': [0, 3, 1, -1, 4, 2]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="2"/>
     <x v="1"/>
     <x v="5"/>
@@ -7992,9 +7998,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [4, 2, -1, 0, 3, 1]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="1"/>
     <x v="4"/>
@@ -8069,9 +8075,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 3, 1, -1, 4, 2]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="1"/>
     <x v="1"/>
     <x v="5"/>
@@ -8146,9 +8152,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'rev', 'map': [0, 3, 1, -1, 4, 2]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="2"/>
     <x v="1"/>
     <x v="5"/>
@@ -8223,9 +8229,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [4, 2, -1, 0, 3, 1]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="1"/>
     <x v="4"/>
@@ -8300,9 +8306,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 3, 1, -1, 4, 2]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="1"/>
     <x v="1"/>
     <x v="5"/>
@@ -8377,9 +8383,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'rev', 'map': [1, 3, 0, 4, 2, -1]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="2"/>
     <x v="1"/>
     <x v="3"/>
@@ -8454,9 +8460,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 3, 1, -1, 4, 2]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="1"/>
     <x v="5"/>
@@ -8531,9 +8537,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [1, 3, 0, 4, 2, -1]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="1"/>
     <x v="1"/>
     <x v="3"/>
@@ -8608,9 +8614,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'rev', 'map': [1, 3, 0, 4, 2, -1]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="2"/>
     <x v="1"/>
     <x v="3"/>
@@ -8685,9 +8691,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 3, 1, -1, 4, 2]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="1"/>
     <x v="5"/>
@@ -8762,9 +8768,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [1, 3, 0, 4, 2, -1]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="1"/>
     <x v="1"/>
     <x v="3"/>
@@ -8839,9 +8845,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'rev', 'map': [1, 3, 0, 4, 2, -1]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="2"/>
     <x v="1"/>
     <x v="3"/>
@@ -8916,9 +8922,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [1, 3, 0, 4, 2, -1]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="1"/>
     <x v="1"/>
     <x v="3"/>
@@ -8993,9 +8999,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 3, 1, -1, 4, 2]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="1"/>
     <x v="5"/>
@@ -9070,9 +9076,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'rev', 'map': [-1, 0, 1, 2, 3, 4]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="2"/>
     <x v="0"/>
     <x v="1"/>
@@ -9147,9 +9153,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [1, 3, 0, 4, 2, -1]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="1"/>
     <x v="3"/>
@@ -9224,9 +9230,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'rev', 'map': [-1, 0, 1, 2, 3, 4]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="2"/>
     <x v="0"/>
     <x v="1"/>
@@ -9301,9 +9307,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [1, 3, 0, 4, 2, -1]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="1"/>
     <x v="3"/>
@@ -9378,9 +9384,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [1, 3, 0, 4, 2, -1]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="1"/>
     <x v="3"/>
@@ -9455,9 +9461,9 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [-1, 0, 1, 2, 3, 4]}]"/>
-    <n v="1"/>
-    <s v="serial"/>
-    <s v="effsu2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="1"/>
     <x v="0"/>
     <x v="1"/>
@@ -9518,7 +9524,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{37B8E839-F96B-4695-BBD4-28D863AD6E55}" name="TablaDinámica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{37B8E839-F96B-4695-BBD4-28D863AD6E55}" name="TablaDinámica1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:L64" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="75">
     <pivotField numFmtId="164" showAll="0"/>
@@ -9545,9 +9551,24 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField axis="axisRow" showAll="0">
       <items count="4">
         <item x="0"/>
